--- a/docs/xlsx/jobs-2026-09-25.xlsx
+++ b/docs/xlsx/jobs-2026-09-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="592">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1765 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Bycatch Analyst</t>
+  </si>
+  <si>
+    <t>Azura Consulting LLC</t>
+  </si>
+  <si>
+    <t>Garland, TX</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$37.13 per hour</t>
+  </si>
+  <si>
+    <t>fisheries-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-bycatch-analyst-garland-texas/1430467169</t>
+  </si>
+  <si>
+    <t>Civil or Water Resources Engineer</t>
+  </si>
+  <si>
+    <t>Ducks Unlimited</t>
+  </si>
+  <si>
+    <t>Syracuse, NY</t>
+  </si>
+  <si>
+    <t>$110,000 - $130,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-civil-or-water-resources-engineer-syracuse-new-york/1383271072</t>
+  </si>
+  <si>
+    <t>Community Forestry Associate (San Fernando Valley)</t>
+  </si>
+  <si>
+    <t>TreePeople</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$22 per hour</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-forestry-associate-san-fernando-valley-los-angeles-california/2897146026</t>
+  </si>
+  <si>
+    <t>Community Forestry Associate (South and Southeast Los Angeles)</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-forestry-associate-south-and-southeast-los-angeles-los-angeles-california/8115116853</t>
+  </si>
+  <si>
+    <t>Conservation Associate</t>
+  </si>
+  <si>
+    <t>Maine Coast Heritage Trust</t>
+  </si>
+  <si>
+    <t>Mount Desert, ME</t>
+  </si>
+  <si>
+    <t>$49,000 - $56,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-associate-mount-desert-maine/5420081894</t>
+  </si>
+  <si>
+    <t>Director of Facilities</t>
+  </si>
+  <si>
+    <t>Pacific Wildlife Care</t>
+  </si>
+  <si>
+    <t>San Luis Obispo, CA</t>
+  </si>
+  <si>
+    <t>$25 - $30 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-facilities-san-luis-obispo-california/9783508356</t>
+  </si>
+  <si>
+    <t>ECDP Natural Resources Technician - Altus Air Force Base, OK</t>
+  </si>
+  <si>
+    <t>Colorado State University - Center for Environmental Management of Military Lands</t>
+  </si>
+  <si>
+    <t>Altus Air Force Base, OK</t>
+  </si>
+  <si>
+    <t>$43,000 - $45,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ecdp-natural-resources-technician---altus-air-force-base-ok-altus-air-force-base-oklahoma/3826629859</t>
+  </si>
+  <si>
+    <t>ECDP Natural Resources Technician - Fort AP Hill, VA</t>
+  </si>
+  <si>
+    <t>Fort AP Hill, VA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ecdp-natural-resources-technician---fort-ap-hill-va-fort-ap-hill-virginia/6501763448</t>
+  </si>
+  <si>
+    <t>Environmental Education Internship</t>
+  </si>
+  <si>
+    <t>Fossil Rim Wildlife Center</t>
+  </si>
+  <si>
+    <t>Glen Rose, TX</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$400 per month</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-education-internship-glen-rose-texas/8038606240</t>
+  </si>
+  <si>
+    <t>EPA Quantifying the Impact of Chemical Exposure on the Thyroid System of Developing Amphibians</t>
+  </si>
+  <si>
+    <t>U.S. Environmental Protection Agency (EPA)</t>
+  </si>
+  <si>
+    <t>Duluth, MN</t>
+  </si>
+  <si>
+    <t>The participant will receive a monthly stipend commensurate with educational level and experience.</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-epa-quantifying-the-impact-of-chemical-exposure-on-the-thyroid-system-of-developing-amphibians-duluth-minnesota/1599143646</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Ammonoosuc Conservation Trust</t>
+  </si>
+  <si>
+    <t>Franconia, NH</t>
+  </si>
+  <si>
+    <t>$80,000 - $95,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-franconia-new-hampshire/3317738152</t>
+  </si>
+  <si>
+    <t>Field Instructor/Lead Instructor</t>
+  </si>
+  <si>
+    <t>Teton Science Schools</t>
+  </si>
+  <si>
+    <t>Jackson, WY</t>
+  </si>
+  <si>
+    <t>$18.80 - $20.65 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-instructorlead-instructor-jackson-wyoming/6582872506</t>
+  </si>
+  <si>
+    <t>Fisheries &amp; Wildlife Bio Scientist II</t>
+  </si>
+  <si>
+    <t>Florida Fish and Wildlife Conservation Commission</t>
+  </si>
+  <si>
+    <t>Sunrise, FL</t>
+  </si>
+  <si>
+    <t>$788.46 per week</t>
+  </si>
+  <si>
+    <t>botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries--wildlife-bio-scientist-ii-sunrise-florida/9184251103</t>
+  </si>
+  <si>
+    <t>Fisheries Technician 2- Wild Salmon and Steelhead Program</t>
+  </si>
+  <si>
+    <t>Pacific States Marine Fisheries Commission</t>
+  </si>
+  <si>
+    <t>McCall, ID</t>
+  </si>
+  <si>
+    <t>$21.61 - $31.54 per hour</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries-technician-2--wild-salmon-and-steelhead-program-mccall-idaho/9543139104</t>
+  </si>
+  <si>
+    <t>Fort Monroe Chesapeake Gateways Ambassador</t>
+  </si>
+  <si>
+    <t>Appalachian Conservation Corps and the National Park Service</t>
+  </si>
+  <si>
+    <t>Hampton, VA</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$760 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fort-monroe-chesapeake-gateways-ambassador-hampton-virginia/6103406732</t>
+  </si>
+  <si>
+    <t>Hatchery Operations Manager - Region 4 Central - WMS Band 2 - Permanent - 2026-06664</t>
+  </si>
+  <si>
+    <t>Washington Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Sultan, WA</t>
+  </si>
+  <si>
+    <t>$110,424 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hatchery-operations-manager---region-4-central---wms-band-2---permanent---2026-06664-sultan-washington/4645755356</t>
+  </si>
+  <si>
+    <t>Land Use Coordinator</t>
+  </si>
+  <si>
+    <t>Colorado Parks &amp; Wildlife</t>
+  </si>
+  <si>
+    <t>Grand Junction, CO</t>
+  </si>
+  <si>
+    <t>$75,888 - $98,640 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-land-use-coordinator-grand-junction-colorado/9926910610</t>
+  </si>
+  <si>
+    <t>Lead Project Forester</t>
+  </si>
+  <si>
+    <t>Colorado State Forest Service</t>
+  </si>
+  <si>
+    <t>Steamboat Springs, CO</t>
+  </si>
+  <si>
+    <t>$60,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-lead-project-forester-steamboat-springs-colorado/9151714997</t>
+  </si>
+  <si>
+    <t>Natural Resources Labor Relations Specialist</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$61,332 - $102,996 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-labor-relations-specialist-olympia-washington/1509409692</t>
+  </si>
+  <si>
+    <t>Operations Associate</t>
+  </si>
+  <si>
+    <t>Backcountry Hunters &amp; Anglers</t>
+  </si>
+  <si>
+    <t>Missoula, MT</t>
+  </si>
+  <si>
+    <t>$45,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations-associate-missoula-montana/8016013187</t>
+  </si>
+  <si>
+    <t>Philanthropy Officer</t>
+  </si>
+  <si>
+    <t>Florida Wildlife Federation</t>
+  </si>
+  <si>
+    <t>Remote from anywhere in the state, FL</t>
+  </si>
+  <si>
+    <t>$70,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-philanthropy-officer-remote-from-anywhere-in-the-state-florida/3078771876</t>
+  </si>
+  <si>
+    <t>Regional Lands Specialist</t>
+  </si>
+  <si>
+    <t>Dexter, MI</t>
+  </si>
+  <si>
+    <t>$65,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regional-lands-specialist-dexter-michigan/1276099118</t>
+  </si>
+  <si>
+    <t>Senior Administrative Specialist</t>
+  </si>
+  <si>
+    <t>Kent Conservation District</t>
+  </si>
+  <si>
+    <t>Dover, DE</t>
+  </si>
+  <si>
+    <t>$39,873.50 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-administrative-specialist-dover-delaware/6747003843</t>
+  </si>
+  <si>
+    <t>Senior Engineering Technician</t>
+  </si>
+  <si>
+    <t>$65,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-engineering-technician-dexter-michigan/1950097220</t>
+  </si>
+  <si>
+    <t>Senior Planner - Natural Resources Environmental Protection Department</t>
+  </si>
+  <si>
+    <t>Alachua County</t>
+  </si>
+  <si>
+    <t>Gainesville, FL</t>
+  </si>
+  <si>
+    <t>$76,564.80 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-planner---natural-resources-environmental-protection-department-gainesville-florida/9828447872</t>
+  </si>
+  <si>
+    <t>Senior Regional Manager of Community Forestry (West)</t>
+  </si>
+  <si>
+    <t>$80,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-regional-manager-of-community-forestry-west-los-angeles-california/2144855220</t>
+  </si>
+  <si>
+    <t>Soil Scientist</t>
+  </si>
+  <si>
+    <t>Provost &amp; Pritchard Consulting Group</t>
+  </si>
+  <si>
+    <t>Visalia, CA</t>
+  </si>
+  <si>
+    <t>$35 - $50 per hour</t>
+  </si>
+  <si>
+    <t>botany-ecology-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-soil-scientist-visalia-california/8179741430</t>
+  </si>
+  <si>
+    <t>USDA-ARS Biological Science Fellowship - Entomology Focus</t>
+  </si>
+  <si>
+    <t>U.S. Department of Agriculture (USDA)</t>
+  </si>
+  <si>
+    <t>Maricopa, AZ</t>
+  </si>
+  <si>
+    <t>Stipend $42,000.00 – $48,000.00 Yearly</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-biological-science-fellowship---entomology-focus-maricopa-arizona/5205714995</t>
+  </si>
+  <si>
+    <t>USDA-ARS Research Fellow for Biological Control of Emerald Ash Borer</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>Stipend $39,000.00 – $45,000.00 Yearly</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-research-fellow-for-biological-control-of-emerald-ash-borer-na-remote/9691000316</t>
+  </si>
+  <si>
+    <t>USDA-ARS SCINet/AI-COE Postdoctoral Fellowship in AI Analysis of UAV Imagery for Rangeland Ecology</t>
+  </si>
+  <si>
+    <t>Burns, OR</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>Stipend $100,000.00 – $110,000.00 Yearly</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-scinetai-coe-postdoctoral-fellowship-in-ai-analysis-of-uav-imagery-for-rangeland-ecology-burns-oregon/8941521801</t>
+  </si>
+  <si>
+    <t>USDA-FS Evaluating Deterrent Systems for Bats</t>
+  </si>
+  <si>
+    <t>Arcata, CA</t>
+  </si>
+  <si>
+    <t>$3,700.00 – $4,500.00 Monthly</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-fs-evaluating-deterrent-systems-for-bats-arcata-california/7674146794</t>
+  </si>
+  <si>
+    <t>USDA-FS Scaling Canine VOC Detection for CRB Biosecurity in Hawai'i</t>
+  </si>
+  <si>
+    <t>Hilo, HI</t>
+  </si>
+  <si>
+    <t>Stipend $3,815.00 – $4,115.00 Monthly</t>
+  </si>
+  <si>
+    <t>ecology-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-fs-scaling-canine-voc-detection-for-crb-biosecurity-in-hawaii-hilo-hawaii/7236430441</t>
+  </si>
+  <si>
+    <t>Wildlife Rehabilitation Assistant</t>
+  </si>
+  <si>
+    <t>Wild Instincts</t>
+  </si>
+  <si>
+    <t>Rhinelander, WI</t>
+  </si>
+  <si>
+    <t>$26,500 - $36,700 per year</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-rehabilitation-assistant-rhinelander-wisconsin/4630344568</t>
+  </si>
+  <si>
+    <t>Youth Programs Manager</t>
+  </si>
+  <si>
+    <t>CitySprouts</t>
+  </si>
+  <si>
+    <t>Cambridge, MA</t>
+  </si>
+  <si>
+    <t>$60,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-youth-programs-manager-cambridge-massachusetts/5365228703</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>Human Rights Watch</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b41f3e5044b4051be3e0f2524050ac4-accountant-human-rights-watch-new-york</t>
+  </si>
+  <si>
+    <t>Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Mathematical Staircase, Inc.</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 25.10/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/481e10cd7aaa4ebc8ad6e1a51943c3c9-administrative-assistant-mathematical-staircase-inc-ardmore</t>
+  </si>
+  <si>
+    <t>Admissions Manager - Mattapan Residential (Casual)</t>
+  </si>
+  <si>
+    <t>Boston Public Health Commission</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 45.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a8c2744a91c4ee4ba162b139f8af72e-admissions-manager-mattapan-residential-casual-boston-public-health-commission-boston</t>
+  </si>
+  <si>
+    <t>Agente en vía pública | CABA y GBA</t>
+  </si>
+  <si>
+    <t>Aldeas Infantiles SOS Argentina</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/88cf4bb3fa4647b380c3d0a1affcf17f-agente-en-via-publica-caba-y-gba-aldeas-infantiles-sos-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General</t>
+  </si>
+  <si>
+    <t>Office of the Massachusetts Attorney General</t>
+  </si>
+  <si>
+    <t>USD 90125.00 - 134513.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/87786b89c81a4c559d0e951160c2b390-assistant-attorney-general-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
+    <t>Associate Director Seattle, Washington</t>
+  </si>
+  <si>
+    <t>AJC</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 103000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Human Rights Civil Liberties, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/76cac6e0f946450f9ff48f4497675cf0-associate-director-seattle-washington-ajc-seattle</t>
+  </si>
+  <si>
+    <t>Associate Director, Development &amp; Outreach</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 102000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ddd3798fda524567a6a16afb06e8b565-associate-director-development-outreach-human-rights-watch-los-angeles</t>
+  </si>
+  <si>
+    <t>Associate Director, Institutional Giving</t>
+  </si>
+  <si>
+    <t>Asia Society</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/88a94875e85940248ee3ffbd1ef39b8f-associate-director-institutional-giving-asia-society-new-york</t>
+  </si>
+  <si>
+    <t>Auxiliar de Cozinha e Limpeza (CLT)</t>
+  </si>
+  <si>
+    <t>Eco Caminhos</t>
+  </si>
+  <si>
+    <t>Nova Friburgo, Rio de Janeiro, BR</t>
+  </si>
+  <si>
+    <t>Agriculture, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d51b1fde21b4ad2852268471e10508e-auxiliar-de-cozinha-e-limpeza-clt-eco-caminhos-nova-friburgo</t>
+  </si>
+  <si>
+    <t>Brooklyn: Director of Development</t>
+  </si>
+  <si>
+    <t>Jeremiah Program_Minneapolis</t>
+  </si>
+  <si>
+    <t>USD 92000.00 - 103000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/737b4fbebe9f435c8c8b765ad6da36b4-brooklyn-director-of-development-jeremiah-programminneapolis-new-york</t>
+  </si>
+  <si>
+    <t>Case Manager</t>
+  </si>
+  <si>
+    <t>Springwell, Inc.</t>
+  </si>
+  <si>
+    <t>Marlborough, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 28.21 - 28.21/hour</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c4b2f979995a4e2697375e0e071e4a9b-case-manager-springwell-inc-marlborough</t>
+  </si>
+  <si>
+    <t>Chief Marketing Officer</t>
+  </si>
+  <si>
+    <t>Leadership Greater Chicago</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ac881ec560064737bd7b7646e2b51a4a-chief-marketing-officer-leadership-greater-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Clinical Supervisor - LaGrange</t>
+  </si>
+  <si>
+    <t>St. Francis House</t>
+  </si>
+  <si>
+    <t>USD 83232.00 - 91011.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60957ada220d42dbab8e49fbf07646ce-clinical-supervisor-lagrange-st-francis-house-boston</t>
+  </si>
+  <si>
+    <t>Communications Coordinator</t>
+  </si>
+  <si>
+    <t>Nurturing Minds, Inc</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Poverty, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ffe52c50d0bf4e82aa121191a1b222b7-communications-coordinator-nurturing-minds-inc-newtonville</t>
+  </si>
+  <si>
+    <t>Community Advocacy Specialist</t>
+  </si>
+  <si>
+    <t>Brookview House, Inc.</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94645c83bcc14d0ca89dd6e3098bc2f4-community-advocacy-specialist-brookview-house-inc-boston</t>
+  </si>
+  <si>
+    <t>Community Education Intern</t>
+  </si>
+  <si>
+    <t>NYC Campaign Finance Board</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5e597a3507ce49a5bb070b0369ebd0e6-community-education-intern-nyc-campaign-finance-board-new-york</t>
+  </si>
+  <si>
+    <t>Community Outreach Intern</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/8e5055962c2648409e897d02bc5b0d78-community-outreach-intern-nyc-campaign-finance-board-new-york</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>PaintCare &amp; American Coatings Association</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b356a9703fef414c8bf13abea14d0cdb-controller-paintcare-american-coatings-association-washington</t>
+  </si>
+  <si>
+    <t>Creative Communications Associate</t>
+  </si>
+  <si>
+    <t>Advance Maryland</t>
+  </si>
+  <si>
+    <t>Remote (Maryland)</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Reproductive Health Rights, Crime Safety, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a524ac3ca6484d25bbdc8035ab261169-creative-communications-associate-advance-maryland-arnold</t>
+  </si>
+  <si>
+    <t>Data Specialist, Impact Team</t>
+  </si>
+  <si>
+    <t>The Jewish Federation of Greater Washington</t>
+  </si>
+  <si>
+    <t>N. Bethesda, MD</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7e766b7cb68c43c6a6a767261b19f920-data-specialist-impact-team-the-jewish-federation-of-greater-washington-n-bethesda</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Catholic Charities of Oregon</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2963c5b129942c6b45d733530bd261b-development-director-catholic-charities-of-oregon-portland</t>
+  </si>
+  <si>
+    <t>International Rescue Committee - Sacramento</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>USD 109416.00 - 109416.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45e9c313f5c74822a99e799b2b47f23c-development-director-international-rescue-committee-sacramento-sacramento</t>
+  </si>
+  <si>
+    <t>Director of Budget and Analysis</t>
+  </si>
+  <si>
+    <t>The Community Group</t>
+  </si>
+  <si>
+    <t>Lawrence, MA</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 149000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d0066b8478f545409b936ae23435971c-director-of-budget-and-analysis-the-community-group-lawrence</t>
+  </si>
+  <si>
+    <t>Director of Capital Projects</t>
+  </si>
+  <si>
+    <t>HeartShare Human Services of New York</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/901e0ec5ec8e4c4ca9445edede73e0b2-director-of-capital-projects-heartshare-human-services-of-new-york-brooklyn</t>
+  </si>
+  <si>
+    <t>Director of Communications</t>
+  </si>
+  <si>
+    <t>Legal Services Corporation</t>
+  </si>
+  <si>
+    <t>USD 167257.00 - 174015.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Civic Engagement, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b635ca0d51c54274a3a595c8832ae4be-director-of-communications-legal-services-corporation-washington</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Transportation Alternatives</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Transportation, Policy, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e3127125ed4948c88fd29a99b668c944-director-of-development-transportation-alternatives-new-york</t>
+  </si>
+  <si>
+    <t>Director of Email and SMS Campaigns</t>
+  </si>
+  <si>
+    <t>Everytown For Gun Safety</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de1bffe8c81c41388eebf96cacf64433-director-of-email-and-sms-campaigns-everytown-for-gun-safety-new-york</t>
+  </si>
+  <si>
+    <t>Director of People Operations</t>
+  </si>
+  <si>
+    <t>Center for Civic Design</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a8fa8c71dc804cdca0dd3038469a7f6b-director-of-people-operations-center-for-civic-design-cambridge</t>
+  </si>
+  <si>
+    <t>Director of Social Services</t>
+  </si>
+  <si>
+    <t>County of Roanoke</t>
+  </si>
+  <si>
+    <t>Salem, Virginia</t>
+  </si>
+  <si>
+    <t>USD 125517.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/1039104df6ef4d2cbf8569970476ae7e-director-of-social-services-county-of-roanoke-salem</t>
+  </si>
+  <si>
+    <t>Director, Clearinghouse Services</t>
+  </si>
+  <si>
+    <t>Health Resources in Action, Inc.</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/199b8bee8e2d447d8640fb94ff9d5b9a-director-clearinghouse-services-health-resources-in-action-inc-boston</t>
+  </si>
+  <si>
+    <t>Director, Marketing and Communication</t>
+  </si>
+  <si>
+    <t>National Cryptologic Foundation</t>
+  </si>
+  <si>
+    <t>Glen Burnie, Maryland</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a72b5cc394084133ba611771e3a564c0-director-marketing-and-communication-national-cryptologic-foundation-glen-burnie</t>
+  </si>
+  <si>
+    <t>Director, Marketing Strategy</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6467a3fca57e47fd85f1ff5819ac50c9-director-marketing-strategy-the-jewish-federation-of-greater-washington-n-bethesda</t>
+  </si>
+  <si>
+    <t>Coastal Neighbors</t>
+  </si>
+  <si>
+    <t>Dartmouth, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c4ae31feb6c84688b66f160f0420de8e-executive-director-coastal-neighbors-dartmouth</t>
+  </si>
+  <si>
+    <t>Executive Director, Dress for Success Greater New York City</t>
+  </si>
+  <si>
+    <t>Dress for Success Worldwide</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Job Workplace, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b528d82cc4e944c8b7602cee0a4d7854-executive-director-dress-for-success-greater-new-york-city-dress-for-success-worldwide-new-york</t>
+  </si>
+  <si>
+    <t>Executive Director/Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>National Association of Counsel for Children (NACC)</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Crime Safety, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75f7c37dd95f4f5bb68b0b8391d962f3-executive-directorchief-executive-officer-national-association-of-counsel-for-children-nacc-denver</t>
+  </si>
+  <si>
+    <t>Facilitador/a Educativo/a en CDMX/ Edo. Mex( Presencial)</t>
+  </si>
+  <si>
+    <t>Educación para Compartir - México</t>
+  </si>
+  <si>
+    <t>Ciudad de México, Ciudad de México, MX</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>MXN 15000.00 - 15000.00/month</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb9f4d565c27423b9aef1849853bc378-facilitadora-educativoa-en-cdmx-edo-mex-presencial-educacion-para-compartir-mexico-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>Foster Care Licensing and Placement Specialist</t>
+  </si>
+  <si>
+    <t>University of South Dakota</t>
+  </si>
+  <si>
+    <t>Vermillion, South Dakota</t>
+  </si>
+  <si>
+    <t>USD 23.56 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ab48e4513e20492bb7786395a5cd76b6-foster-care-licensing-and-placement-specialist-university-of-south-dakota-vermillion</t>
+  </si>
+  <si>
+    <t>Funder Relations Manager</t>
+  </si>
+  <si>
+    <t>The Center for Cultural Power</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Climate Change, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bb716ff1f6794b5bba41ccc7b7cfd9ba-funder-relations-manager-the-center-for-cultural-power-oakland</t>
+  </si>
+  <si>
+    <t>Geriatric Support Services Coordinator</t>
+  </si>
+  <si>
+    <t>Disability, Seniors Retirement, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/42680ae446ba4f7ca58fcbc38b5cd456-geriatric-support-services-coordinator-springwell-inc-marlborough</t>
+  </si>
+  <si>
+    <t>Government Affairs Coordinator</t>
+  </si>
+  <si>
+    <t>Riverkeeper</t>
+  </si>
+  <si>
+    <t>Ossining, NY</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b372460713df4427bc2e16d9660bd23f-government-affairs-coordinator-riverkeeper-ossining</t>
+  </si>
+  <si>
+    <t>Health Counselor</t>
+  </si>
+  <si>
+    <t>CSSNY</t>
+  </si>
+  <si>
+    <t>USD 85395.00 - 85395.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Mental Health, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1315218897ec42ee96a9844861ca98f4-health-counselor-cssny-new-york</t>
+  </si>
+  <si>
+    <t>HR Worker Care Manager</t>
+  </si>
+  <si>
+    <t>Mennonite Central Committee</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 87000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61dc965e64ac4abe8a1e369c2fc84784-hr-worker-care-manager-mennonite-central-committee-akron</t>
+  </si>
+  <si>
+    <t>Human Resources Assistant (Part-Time)</t>
+  </si>
+  <si>
+    <t>Carnegie Endowment for International Peace</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f01e6d8f773043eba056948f780f7346-human-resources-assistant-part-time-carnegie-endowment-for-international-peace-washington</t>
+  </si>
+  <si>
+    <t>Hypothermia Shelter Coordinator</t>
+  </si>
+  <si>
+    <t>Rising Hope United Methodist Mission Church</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Poverty, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9866ea3581554261890539551439fbcb-hypothermia-shelter-coordinator-rising-hope-united-methodist-mission-church-alexandria</t>
+  </si>
+  <si>
+    <t>Individual Giving Manager</t>
+  </si>
+  <si>
+    <t>Democracy Now! Productions</t>
+  </si>
+  <si>
+    <t>USD 83300.00 - 86000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae6fb015071c44cc935feda85a1ade4f-individual-giving-manager-democracy-now-productions-new-york</t>
+  </si>
+  <si>
+    <t>Key Account Manager (Industry)</t>
+  </si>
+  <si>
+    <t>Lead Exposure Elimination Project</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a597136d302040e5a137000b4c13cb6f-key-account-manager-industry-lead-exposure-elimination-project-london</t>
+  </si>
+  <si>
+    <t>Lead Mentor</t>
+  </si>
+  <si>
+    <t>Big Brothers Big Sisters of Eastern Missouri</t>
+  </si>
+  <si>
+    <t>St. Louis, Missouri</t>
+  </si>
+  <si>
+    <t>USD 44000.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba6949dbee664d54be6e1ef6b11a2bee-lead-mentor-big-brothers-big-sisters-of-eastern-missouri-st-louis</t>
+  </si>
+  <si>
+    <t>Major Donor Associate</t>
+  </si>
+  <si>
+    <t>Maryknoll Sisters</t>
+  </si>
+  <si>
+    <t>Ossining, New York</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a2e79d71133c4322a35c2dd70cf96608-major-donor-associate-maryknoll-sisters-ossining</t>
+  </si>
+  <si>
+    <t>Major Gifts and Planned Giving Manager</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Children Youth, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a01a88a7b1d94873900796affefe245a-major-gifts-and-planned-giving-manager-maryknoll-sisters-ossining</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>Reproductive Freedom for All</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Policy, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30884d5ca1084ae5b510b97e9b018546-major-gifts-officer-reproductive-freedom-for-all-san-francisco</t>
+  </si>
+  <si>
+    <t>Manager of Intergenerational Programs</t>
+  </si>
+  <si>
+    <t>Openhouse</t>
+  </si>
+  <si>
+    <t>USD 72500.00 - 73900.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Lgbtq, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/957ab7c5401845abae0730d408bc6c42-manager-of-intergenerational-programs-openhouse-san-francisco</t>
+  </si>
+  <si>
+    <t>Managing Director</t>
+  </si>
+  <si>
+    <t>USD 180000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58832529cb2b43ffb776b9323d6a1254-managing-director-transportation-alternatives-new-york</t>
+  </si>
+  <si>
+    <t>Mentoring Case Manager</t>
+  </si>
+  <si>
+    <t>St. Peters, Missouri</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/10bf00c2564c41578168d3d757cbfda2-mentoring-case-manager-big-brothers-big-sisters-of-eastern-missouri-st-peters</t>
+  </si>
+  <si>
+    <t>Middle School After-school Site Director</t>
+  </si>
+  <si>
+    <t>Manhattan Youth Recreation and Resources, Inc.</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/113c9c1ef7b841e6934b5a55af5dca9b-middle-school-after-school-site-director-manhattan-youth-recreation-and-resources-inc-new-york</t>
+  </si>
+  <si>
+    <t>Office and Events Manager</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee6fbbddd19046fc87194a224fc810ad-office-and-events-manager-asia-society-washington</t>
+  </si>
+  <si>
+    <t>Operations &amp; Development Consultant (Independent Contractor, Remote)</t>
+  </si>
+  <si>
+    <t>American Diabetes Society</t>
+  </si>
+  <si>
+    <t>USD 6000.00 - 6000.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c2513ac64b64705b2b3ed122fa5a8e6-operations-development-consultant-independent-contractor-remote-american-diabetes-society-bellaire</t>
+  </si>
+  <si>
+    <t>Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Evanston RoundTable</t>
+  </si>
+  <si>
+    <t>Evanston, Illinois</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78e871e8e91f4de49f42868bdee5f3e3-operations-coordinator-evanston-roundtable-evanston</t>
+  </si>
+  <si>
+    <t>Operations Specialist</t>
+  </si>
+  <si>
+    <t>CaringKind, Your Trusted Partner in Alzheimer's and Dementia Care</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d526842f5ace460a87a68e06b157775b-operations-specialist-caringkind-your-trusted-partner-in-alzheimers-and-dementia-care-new-york</t>
+  </si>
+  <si>
+    <t>Part-time ESL Instructor</t>
+  </si>
+  <si>
+    <t>Arab American Association of New York</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1631192f072844c18c571dbe75121ef5-part-time-esl-instructor-arab-american-association-of-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Preschool Teacher ($500 Sign on Bonus)</t>
+  </si>
+  <si>
+    <t>Burlington Children's Space</t>
+  </si>
+  <si>
+    <t>Burlington, Vermont</t>
+  </si>
+  <si>
+    <t>USD 22.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7685b3cc83d04768a7885d22b129aa60-preschool-teacher-500-sign-on-bonus-burlington-childrens-space-burlington</t>
+  </si>
+  <si>
+    <t>Program and Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>Books Are Wings</t>
+  </si>
+  <si>
+    <t>Pawtucket, Rhode Island</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9cb394f732d40e482904b004f051d18-program-and-outreach-coordinator-books-are-wings-pawtucket</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>Sunstone Strategies</t>
+  </si>
+  <si>
+    <t>USD 82379.00 - 92677.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/c69bbf71fe8e4eb8b9c91151e11fe327-program-manager-sunstone-strategies-oakland</t>
+  </si>
+  <si>
+    <t>Program Manager, India (Chhattisgarh)</t>
+  </si>
+  <si>
+    <t>Remote (IN)</t>
+  </si>
+  <si>
+    <t>INR 4289639.00 - 4575615.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba7e65705785401e84013cbdf924df84-program-manager-india-chhattisgarh-lead-exposure-elimination-project-london</t>
+  </si>
+  <si>
+    <t>Program Manager, India (Uttar Pradesh)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5cf5181c183d49ae8f448cc785979571-program-manager-india-uttar-pradesh-lead-exposure-elimination-project-london</t>
+  </si>
+  <si>
+    <t>Rapid Response Paralegal</t>
+  </si>
+  <si>
+    <t>New York Legal Assistance Group (NYLAG)</t>
+  </si>
+  <si>
+    <t>USD 67793.00 - 72442.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a996535c86bf4b76a71e65a332bf5da0-rapid-response-paralegal-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Registered Nurse (RN)</t>
+  </si>
+  <si>
+    <t>Waltham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72ac41fb1e664e4baae6dec942aeb2a5-registered-nurse-rn-springwell-inc-waltham</t>
+  </si>
+  <si>
+    <t>Residence Life Coordinator - LaGrange</t>
+  </si>
+  <si>
+    <t>USD 24.23 - 26.66/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3fbec6e7d4ff423ea6bd1c4d029fd8eb-residence-life-coordinator-lagrange-st-francis-house-boston</t>
+  </si>
+  <si>
+    <t>School Based Mentoring Program - Program Specialist</t>
+  </si>
+  <si>
+    <t>Big Brothers Big Sisters of Greater Los Angeles</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a4d115c4caa46ed93696d2748a0863e-school-based-mentoring-program-program-specialist-big-brothers-big-sisters-of-greater-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Senior Data Engineer - Tech Equity Fellowship</t>
+  </si>
+  <si>
+    <t>Code the Dream</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45dc48c85db84746a42e84172eb2ea39-senior-data-engineer-tech-equity-fellowship-code-the-dream-durham</t>
+  </si>
+  <si>
+    <t>Senior Director of Family and Community Programs</t>
+  </si>
+  <si>
+    <t>Family Nurturing Center of MA</t>
+  </si>
+  <si>
+    <t>Dorchester, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 106000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a20c3edef10a4ecfb69f766f7ef1536e-senior-director-of-family-and-community-programs-family-nurturing-center-of-ma-dorchester</t>
+  </si>
+  <si>
+    <t>Senior Director of People and Culture</t>
+  </si>
+  <si>
+    <t>USD 98000.00 - 106000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c92e415494d4b2bbeb1f74cb206002c-senior-director-of-people-and-culture-family-nurturing-center-of-ma-dorchester</t>
+  </si>
+  <si>
+    <t>Senior Policy Analyst, Health Policy</t>
+  </si>
+  <si>
+    <t>Center for American Progress</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 84000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Health Medicine, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/95091757bfde498588fe622dd1240f06-senior-policy-analyst-health-policy-center-for-american-progress-washington</t>
+  </si>
+  <si>
+    <t>Specialist, Exploration Technology Lab</t>
+  </si>
+  <si>
+    <t>National Geographic Society</t>
+  </si>
+  <si>
+    <t>USD 71250.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/56ae7c2df91648f58f3c75a5342d80bb-specialist-exploration-technology-lab-national-geographic-society-washington</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>New York State Nurses Association</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4c9e53bb992479ea90272b121a8b5e6-staff-accountant-new-york-state-nurses-association-albany</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 90262.00 - 104544.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7516948e35f94881a6dadb4d5b49c5e3-staff-attorney-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Staff or Sr. Staff Attorney - Child and Youth Rights Facilities and Community</t>
+  </si>
+  <si>
+    <t>National Disability Rights Network (NDRN)</t>
+  </si>
+  <si>
+    <t>USD 83000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/409e9658201b42b4ab66637c32387f8b-staff-or-sr-staff-attorney-child-and-youth-rights-facilities-and-community-national-disability-rights-network-ndrn-washington</t>
+  </si>
+  <si>
+    <t>Stop Data Centers Canvasser</t>
+  </si>
+  <si>
+    <t>Food &amp; Water Watch</t>
+  </si>
+  <si>
+    <t>Remote (Allentown, Pennsylvania)</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Consumer Protection, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dab0c58846984b89948ceb5907508cf1-stop-data-centers-canvasser-food-water-watch-allentown</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d720c33a3754ea9aaac2695c5fd7e73-stop-data-centers-canvasser-food-water-watch-yonkers</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50c8ec93dcf342999a6e0d98b35e38cf-supervisor-springwell-inc-waltham</t>
+  </si>
+  <si>
+    <t>Systems Reliability Engineer</t>
+  </si>
+  <si>
+    <t>Local Public, a Public Benefit Corporation</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/7d122619375b4a6485c641166c65d3af-systems-reliability-engineer-local-public-a-public-benefit-corporation-seattle</t>
+  </si>
+  <si>
+    <t>Temporary Immigration Attorney</t>
+  </si>
+  <si>
+    <t>USD 87944.00 - 100532.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f02d4747c0454a87b7a98ddf21503289-temporary-immigration-attorney-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Upward Mentoring Manager – Part Time</t>
+  </si>
+  <si>
+    <t>USD 21.15 - 22.15/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a3ada64004bf46f897cd865166549fec-upward-mentoring-manager-part-time-big-brothers-big-sisters-of-eastern-missouri-st-louis</t>
+  </si>
+  <si>
+    <t>Youth Program Assistant Instructor</t>
+  </si>
+  <si>
+    <t>Many Languages One Voice</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0859c2e919d5490282a07662dad974ed-youth-program-assistant-instructor-many-languages-one-voice-washington</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1806,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1832,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2175,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2214,826 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" t="s">
+        <v>102</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" t="s">
+        <v>113</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" t="s">
+        <v>113</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" t="s">
+        <v>113</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" t="s">
+        <v>40</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" t="s">
+        <v>113</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>126</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" t="s">
+        <v>139</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>140</v>
+      </c>
+      <c r="F26" t="s">
+        <v>40</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" t="s">
+        <v>143</v>
+      </c>
+      <c r="F27" t="s">
+        <v>144</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" t="s">
+        <v>148</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>149</v>
+      </c>
+      <c r="F28" t="s">
+        <v>150</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>152</v>
+      </c>
+      <c r="B29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" t="s">
+        <v>154</v>
+      </c>
+      <c r="D29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" t="s">
+        <v>155</v>
+      </c>
+      <c r="F29" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>157</v>
+      </c>
+      <c r="B30" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" t="s">
+        <v>158</v>
+      </c>
+      <c r="D30" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" t="s">
+        <v>159</v>
+      </c>
+      <c r="F30" t="s">
+        <v>61</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" t="s">
+        <v>153</v>
+      </c>
+      <c r="C31" t="s">
+        <v>162</v>
+      </c>
+      <c r="D31" t="s">
+        <v>163</v>
+      </c>
+      <c r="E31" t="s">
+        <v>164</v>
+      </c>
+      <c r="F31" t="s">
+        <v>165</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>167</v>
+      </c>
+      <c r="B32" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" t="s">
+        <v>168</v>
+      </c>
+      <c r="D32" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" t="s">
+        <v>169</v>
+      </c>
+      <c r="F32" t="s">
+        <v>61</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B33" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" t="s">
+        <v>172</v>
+      </c>
+      <c r="D33" t="s">
+        <v>53</v>
+      </c>
+      <c r="E33" t="s">
+        <v>173</v>
+      </c>
+      <c r="F33" t="s">
+        <v>174</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>176</v>
+      </c>
+      <c r="B34" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" t="s">
+        <v>178</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>179</v>
+      </c>
+      <c r="F34" t="s">
+        <v>180</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>182</v>
+      </c>
+      <c r="B35" t="s">
+        <v>183</v>
+      </c>
+      <c r="C35" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>185</v>
+      </c>
+      <c r="F35" t="s">
+        <v>73</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3089,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3128,2002 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" t="s">
+        <v>205</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" t="s">
+        <v>210</v>
+      </c>
+      <c r="E5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F6" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" t="s">
+        <v>221</v>
+      </c>
+      <c r="F7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D8" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" t="s">
+        <v>226</v>
+      </c>
+      <c r="F8" t="s">
+        <v>192</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" t="s">
+        <v>230</v>
+      </c>
+      <c r="F9" t="s">
+        <v>231</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" t="s">
+        <v>211</v>
+      </c>
+      <c r="F10" t="s">
+        <v>236</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F11" t="s">
+        <v>241</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E12" t="s">
+        <v>246</v>
+      </c>
+      <c r="F12" t="s">
+        <v>247</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" t="s">
+        <v>250</v>
+      </c>
+      <c r="C13" t="s">
+        <v>251</v>
+      </c>
+      <c r="D13" t="s">
+        <v>190</v>
+      </c>
+      <c r="E13" t="s">
+        <v>252</v>
+      </c>
+      <c r="F13" t="s">
+        <v>253</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>255</v>
+      </c>
+      <c r="B14" t="s">
+        <v>256</v>
+      </c>
+      <c r="C14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" t="s">
+        <v>257</v>
+      </c>
+      <c r="F14" t="s">
+        <v>258</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B15" t="s">
+        <v>261</v>
+      </c>
+      <c r="C15" t="s">
+        <v>196</v>
+      </c>
+      <c r="D15" t="s">
+        <v>190</v>
+      </c>
+      <c r="E15" t="s">
+        <v>262</v>
+      </c>
+      <c r="F15" t="s">
+        <v>263</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>265</v>
+      </c>
+      <c r="B16" t="s">
+        <v>266</v>
+      </c>
+      <c r="C16" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E16" t="s">
+        <v>267</v>
+      </c>
+      <c r="F16" t="s">
+        <v>268</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>270</v>
+      </c>
+      <c r="B17" t="s">
+        <v>271</v>
+      </c>
+      <c r="C17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17" t="s">
+        <v>197</v>
+      </c>
+      <c r="E17" t="s">
+        <v>211</v>
+      </c>
+      <c r="F17" t="s">
+        <v>272</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>274</v>
+      </c>
+      <c r="B18" t="s">
+        <v>271</v>
+      </c>
+      <c r="C18" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" t="s">
+        <v>197</v>
+      </c>
+      <c r="E18" t="s">
+        <v>211</v>
+      </c>
+      <c r="F18" t="s">
+        <v>272</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>276</v>
+      </c>
+      <c r="B19" t="s">
+        <v>277</v>
+      </c>
+      <c r="C19" t="s">
+        <v>278</v>
+      </c>
+      <c r="D19" t="s">
+        <v>190</v>
+      </c>
+      <c r="E19" t="s">
+        <v>279</v>
+      </c>
+      <c r="F19" t="s">
+        <v>211</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>281</v>
+      </c>
+      <c r="B20" t="s">
+        <v>282</v>
+      </c>
+      <c r="C20" t="s">
+        <v>283</v>
+      </c>
+      <c r="D20" t="s">
+        <v>190</v>
+      </c>
+      <c r="E20" t="s">
+        <v>284</v>
+      </c>
+      <c r="F20" t="s">
+        <v>285</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>287</v>
+      </c>
+      <c r="B21" t="s">
+        <v>288</v>
+      </c>
+      <c r="C21" t="s">
+        <v>289</v>
+      </c>
+      <c r="D21" t="s">
+        <v>190</v>
+      </c>
+      <c r="E21" t="s">
+        <v>290</v>
+      </c>
+      <c r="F21" t="s">
+        <v>291</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>293</v>
+      </c>
+      <c r="B22" t="s">
+        <v>294</v>
+      </c>
+      <c r="C22" t="s">
+        <v>295</v>
+      </c>
+      <c r="D22" t="s">
+        <v>190</v>
+      </c>
+      <c r="E22" t="s">
+        <v>296</v>
+      </c>
+      <c r="F22" t="s">
+        <v>297</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>293</v>
+      </c>
+      <c r="B23" t="s">
+        <v>299</v>
+      </c>
+      <c r="C23" t="s">
+        <v>300</v>
+      </c>
+      <c r="D23" t="s">
+        <v>190</v>
+      </c>
+      <c r="E23" t="s">
+        <v>301</v>
+      </c>
+      <c r="F23" t="s">
+        <v>302</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>304</v>
+      </c>
+      <c r="B24" t="s">
+        <v>305</v>
+      </c>
+      <c r="C24" t="s">
+        <v>306</v>
+      </c>
+      <c r="D24" t="s">
+        <v>190</v>
+      </c>
+      <c r="E24" t="s">
+        <v>307</v>
+      </c>
+      <c r="F24" t="s">
+        <v>308</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>310</v>
+      </c>
+      <c r="B25" t="s">
+        <v>311</v>
+      </c>
+      <c r="C25" t="s">
+        <v>312</v>
+      </c>
+      <c r="D25" t="s">
+        <v>190</v>
+      </c>
+      <c r="E25" t="s">
+        <v>296</v>
+      </c>
+      <c r="F25" t="s">
+        <v>313</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>315</v>
+      </c>
+      <c r="B26" t="s">
+        <v>316</v>
+      </c>
+      <c r="C26" t="s">
+        <v>278</v>
+      </c>
+      <c r="D26" t="s">
+        <v>190</v>
+      </c>
+      <c r="E26" t="s">
+        <v>317</v>
+      </c>
+      <c r="F26" t="s">
+        <v>318</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>320</v>
+      </c>
+      <c r="B27" t="s">
+        <v>321</v>
+      </c>
+      <c r="C27" t="s">
+        <v>322</v>
+      </c>
+      <c r="D27" t="s">
+        <v>190</v>
+      </c>
+      <c r="E27" t="s">
+        <v>323</v>
+      </c>
+      <c r="F27" t="s">
+        <v>324</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B28" t="s">
+        <v>327</v>
+      </c>
+      <c r="C28" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" t="s">
+        <v>190</v>
+      </c>
+      <c r="E28" t="s">
+        <v>328</v>
+      </c>
+      <c r="F28" t="s">
+        <v>329</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>331</v>
+      </c>
+      <c r="B29" t="s">
+        <v>332</v>
+      </c>
+      <c r="C29" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" t="s">
+        <v>333</v>
+      </c>
+      <c r="F29" t="s">
+        <v>334</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>336</v>
+      </c>
+      <c r="B30" t="s">
+        <v>337</v>
+      </c>
+      <c r="C30" t="s">
+        <v>338</v>
+      </c>
+      <c r="D30" t="s">
+        <v>190</v>
+      </c>
+      <c r="E30" t="s">
+        <v>339</v>
+      </c>
+      <c r="F30" t="s">
+        <v>211</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>341</v>
+      </c>
+      <c r="B31" t="s">
+        <v>342</v>
+      </c>
+      <c r="C31" t="s">
+        <v>203</v>
+      </c>
+      <c r="D31" t="s">
+        <v>190</v>
+      </c>
+      <c r="E31" t="s">
+        <v>343</v>
+      </c>
+      <c r="F31" t="s">
+        <v>211</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>345</v>
+      </c>
+      <c r="B32" t="s">
+        <v>346</v>
+      </c>
+      <c r="C32" t="s">
+        <v>347</v>
+      </c>
+      <c r="D32" t="s">
+        <v>190</v>
+      </c>
+      <c r="E32" t="s">
+        <v>348</v>
+      </c>
+      <c r="F32" t="s">
+        <v>349</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>351</v>
+      </c>
+      <c r="B33" t="s">
+        <v>288</v>
+      </c>
+      <c r="C33" t="s">
+        <v>289</v>
+      </c>
+      <c r="D33" t="s">
+        <v>190</v>
+      </c>
+      <c r="E33" t="s">
+        <v>352</v>
+      </c>
+      <c r="F33" t="s">
+        <v>291</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" t="s">
+        <v>354</v>
+      </c>
+      <c r="C34" t="s">
+        <v>355</v>
+      </c>
+      <c r="D34" t="s">
+        <v>190</v>
+      </c>
+      <c r="E34" t="s">
+        <v>356</v>
+      </c>
+      <c r="F34" t="s">
+        <v>357</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>359</v>
+      </c>
+      <c r="B35" t="s">
+        <v>360</v>
+      </c>
+      <c r="C35" t="s">
+        <v>189</v>
+      </c>
+      <c r="D35" t="s">
+        <v>190</v>
+      </c>
+      <c r="E35" t="s">
+        <v>361</v>
+      </c>
+      <c r="F35" t="s">
+        <v>362</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>364</v>
+      </c>
+      <c r="B36" t="s">
+        <v>365</v>
+      </c>
+      <c r="C36" t="s">
+        <v>196</v>
+      </c>
+      <c r="D36" t="s">
+        <v>190</v>
+      </c>
+      <c r="E36" t="s">
+        <v>366</v>
+      </c>
+      <c r="F36" t="s">
+        <v>367</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>369</v>
+      </c>
+      <c r="B37" t="s">
+        <v>370</v>
+      </c>
+      <c r="C37" t="s">
+        <v>371</v>
+      </c>
+      <c r="D37" t="s">
+        <v>372</v>
+      </c>
+      <c r="E37" t="s">
+        <v>373</v>
+      </c>
+      <c r="F37" t="s">
+        <v>374</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>376</v>
+      </c>
+      <c r="B38" t="s">
+        <v>377</v>
+      </c>
+      <c r="C38" t="s">
+        <v>378</v>
+      </c>
+      <c r="D38" t="s">
+        <v>190</v>
+      </c>
+      <c r="E38" t="s">
+        <v>379</v>
+      </c>
+      <c r="F38" t="s">
+        <v>211</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>381</v>
+      </c>
+      <c r="B39" t="s">
+        <v>382</v>
+      </c>
+      <c r="C39" t="s">
+        <v>196</v>
+      </c>
+      <c r="D39" t="s">
+        <v>190</v>
+      </c>
+      <c r="E39" t="s">
+        <v>383</v>
+      </c>
+      <c r="F39" t="s">
+        <v>384</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>386</v>
+      </c>
+      <c r="B40" t="s">
+        <v>244</v>
+      </c>
+      <c r="C40" t="s">
+        <v>245</v>
+      </c>
+      <c r="D40" t="s">
+        <v>190</v>
+      </c>
+      <c r="E40" t="s">
+        <v>246</v>
+      </c>
+      <c r="F40" t="s">
+        <v>387</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>389</v>
+      </c>
+      <c r="B41" t="s">
+        <v>390</v>
+      </c>
+      <c r="C41" t="s">
+        <v>391</v>
+      </c>
+      <c r="D41" t="s">
+        <v>190</v>
+      </c>
+      <c r="E41" t="s">
+        <v>392</v>
+      </c>
+      <c r="F41" t="s">
+        <v>393</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>395</v>
+      </c>
+      <c r="B42" t="s">
+        <v>396</v>
+      </c>
+      <c r="C42" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" t="s">
+        <v>190</v>
+      </c>
+      <c r="E42" t="s">
+        <v>397</v>
+      </c>
+      <c r="F42" t="s">
+        <v>398</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>400</v>
+      </c>
+      <c r="B43" t="s">
+        <v>401</v>
+      </c>
+      <c r="C43" t="s">
+        <v>196</v>
+      </c>
+      <c r="D43" t="s">
+        <v>190</v>
+      </c>
+      <c r="E43" t="s">
+        <v>402</v>
+      </c>
+      <c r="F43" t="s">
+        <v>403</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>405</v>
+      </c>
+      <c r="B44" t="s">
+        <v>406</v>
+      </c>
+      <c r="C44" t="s">
+        <v>407</v>
+      </c>
+      <c r="D44" t="s">
+        <v>190</v>
+      </c>
+      <c r="E44" t="s">
+        <v>408</v>
+      </c>
+      <c r="F44" t="s">
+        <v>409</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>411</v>
+      </c>
+      <c r="B45" t="s">
+        <v>412</v>
+      </c>
+      <c r="C45" t="s">
+        <v>413</v>
+      </c>
+      <c r="D45" t="s">
+        <v>190</v>
+      </c>
+      <c r="E45" t="s">
+        <v>414</v>
+      </c>
+      <c r="F45" t="s">
+        <v>415</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>417</v>
+      </c>
+      <c r="B46" t="s">
+        <v>418</v>
+      </c>
+      <c r="C46" t="s">
+        <v>189</v>
+      </c>
+      <c r="D46" t="s">
+        <v>190</v>
+      </c>
+      <c r="E46" t="s">
+        <v>419</v>
+      </c>
+      <c r="F46" t="s">
+        <v>211</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>421</v>
+      </c>
+      <c r="B47" t="s">
+        <v>422</v>
+      </c>
+      <c r="C47" t="s">
+        <v>196</v>
+      </c>
+      <c r="D47" t="s">
+        <v>190</v>
+      </c>
+      <c r="E47" t="s">
+        <v>211</v>
+      </c>
+      <c r="F47" t="s">
+        <v>423</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>425</v>
+      </c>
+      <c r="B48" t="s">
+        <v>426</v>
+      </c>
+      <c r="C48" t="s">
+        <v>427</v>
+      </c>
+      <c r="D48" t="s">
+        <v>190</v>
+      </c>
+      <c r="E48" t="s">
+        <v>428</v>
+      </c>
+      <c r="F48" t="s">
+        <v>429</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>431</v>
+      </c>
+      <c r="B49" t="s">
+        <v>432</v>
+      </c>
+      <c r="C49" t="s">
+        <v>433</v>
+      </c>
+      <c r="D49" t="s">
+        <v>190</v>
+      </c>
+      <c r="E49" t="s">
+        <v>434</v>
+      </c>
+      <c r="F49" t="s">
+        <v>435</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>437</v>
+      </c>
+      <c r="B50" t="s">
+        <v>432</v>
+      </c>
+      <c r="C50" t="s">
+        <v>433</v>
+      </c>
+      <c r="D50" t="s">
+        <v>190</v>
+      </c>
+      <c r="E50" t="s">
+        <v>438</v>
+      </c>
+      <c r="F50" t="s">
+        <v>439</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>441</v>
+      </c>
+      <c r="B51" t="s">
+        <v>442</v>
+      </c>
+      <c r="C51" t="s">
+        <v>443</v>
+      </c>
+      <c r="D51" t="s">
+        <v>190</v>
+      </c>
+      <c r="E51" t="s">
+        <v>444</v>
+      </c>
+      <c r="F51" t="s">
+        <v>445</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>447</v>
+      </c>
+      <c r="B52" t="s">
+        <v>448</v>
+      </c>
+      <c r="C52" t="s">
+        <v>443</v>
+      </c>
+      <c r="D52" t="s">
+        <v>190</v>
+      </c>
+      <c r="E52" t="s">
+        <v>449</v>
+      </c>
+      <c r="F52" t="s">
+        <v>450</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>452</v>
+      </c>
+      <c r="B53" t="s">
+        <v>321</v>
+      </c>
+      <c r="C53" t="s">
+        <v>322</v>
+      </c>
+      <c r="D53" t="s">
+        <v>190</v>
+      </c>
+      <c r="E53" t="s">
+        <v>453</v>
+      </c>
+      <c r="F53" t="s">
+        <v>324</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>455</v>
+      </c>
+      <c r="B54" t="s">
+        <v>426</v>
+      </c>
+      <c r="C54" t="s">
+        <v>456</v>
+      </c>
+      <c r="D54" t="s">
+        <v>190</v>
+      </c>
+      <c r="E54" t="s">
+        <v>428</v>
+      </c>
+      <c r="F54" t="s">
+        <v>457</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>459</v>
+      </c>
+      <c r="B55" t="s">
+        <v>460</v>
+      </c>
+      <c r="C55" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55" t="s">
+        <v>190</v>
+      </c>
+      <c r="E55" t="s">
+        <v>461</v>
+      </c>
+      <c r="F55" t="s">
+        <v>462</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>464</v>
+      </c>
+      <c r="B56" t="s">
+        <v>229</v>
+      </c>
+      <c r="C56" t="s">
+        <v>278</v>
+      </c>
+      <c r="D56" t="s">
+        <v>190</v>
+      </c>
+      <c r="E56" t="s">
+        <v>465</v>
+      </c>
+      <c r="F56" t="s">
+        <v>231</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>467</v>
+      </c>
+      <c r="B57" t="s">
+        <v>468</v>
+      </c>
+      <c r="C57" t="s">
+        <v>196</v>
+      </c>
+      <c r="D57" t="s">
+        <v>210</v>
+      </c>
+      <c r="E57" t="s">
+        <v>469</v>
+      </c>
+      <c r="F57" t="s">
+        <v>470</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>472</v>
+      </c>
+      <c r="B58" t="s">
+        <v>473</v>
+      </c>
+      <c r="C58" t="s">
+        <v>474</v>
+      </c>
+      <c r="D58" t="s">
+        <v>197</v>
+      </c>
+      <c r="E58" t="s">
+        <v>475</v>
+      </c>
+      <c r="F58" t="s">
+        <v>476</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>478</v>
+      </c>
+      <c r="B59" t="s">
+        <v>479</v>
+      </c>
+      <c r="C59" t="s">
+        <v>189</v>
+      </c>
+      <c r="D59" t="s">
+        <v>190</v>
+      </c>
+      <c r="E59" t="s">
+        <v>480</v>
+      </c>
+      <c r="F59" t="s">
+        <v>481</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>483</v>
+      </c>
+      <c r="B60" t="s">
+        <v>484</v>
+      </c>
+      <c r="C60" t="s">
+        <v>485</v>
+      </c>
+      <c r="D60" t="s">
+        <v>197</v>
+      </c>
+      <c r="E60" t="s">
+        <v>486</v>
+      </c>
+      <c r="F60" t="s">
+        <v>211</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>488</v>
+      </c>
+      <c r="B61" t="s">
+        <v>489</v>
+      </c>
+      <c r="C61" t="s">
+        <v>490</v>
+      </c>
+      <c r="D61" t="s">
+        <v>190</v>
+      </c>
+      <c r="E61" t="s">
+        <v>491</v>
+      </c>
+      <c r="F61" t="s">
+        <v>492</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>494</v>
+      </c>
+      <c r="B62" t="s">
+        <v>495</v>
+      </c>
+      <c r="C62" t="s">
+        <v>496</v>
+      </c>
+      <c r="D62" t="s">
+        <v>197</v>
+      </c>
+      <c r="E62" t="s">
+        <v>497</v>
+      </c>
+      <c r="F62" t="s">
+        <v>498</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>500</v>
+      </c>
+      <c r="B63" t="s">
+        <v>501</v>
+      </c>
+      <c r="C63" t="s">
+        <v>196</v>
+      </c>
+      <c r="D63" t="s">
+        <v>190</v>
+      </c>
+      <c r="E63" t="s">
+        <v>502</v>
+      </c>
+      <c r="F63" t="s">
+        <v>503</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>505</v>
+      </c>
+      <c r="B64" t="s">
+        <v>422</v>
+      </c>
+      <c r="C64" t="s">
+        <v>506</v>
+      </c>
+      <c r="D64" t="s">
+        <v>190</v>
+      </c>
+      <c r="E64" t="s">
+        <v>507</v>
+      </c>
+      <c r="F64" t="s">
+        <v>423</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>509</v>
+      </c>
+      <c r="B65" t="s">
+        <v>422</v>
+      </c>
+      <c r="C65" t="s">
+        <v>506</v>
+      </c>
+      <c r="D65" t="s">
+        <v>190</v>
+      </c>
+      <c r="E65" t="s">
+        <v>507</v>
+      </c>
+      <c r="F65" t="s">
+        <v>423</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>511</v>
+      </c>
+      <c r="B66" t="s">
+        <v>512</v>
+      </c>
+      <c r="C66" t="s">
+        <v>189</v>
+      </c>
+      <c r="D66" t="s">
+        <v>190</v>
+      </c>
+      <c r="E66" t="s">
+        <v>513</v>
+      </c>
+      <c r="F66" t="s">
+        <v>514</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>516</v>
+      </c>
+      <c r="B67" t="s">
+        <v>244</v>
+      </c>
+      <c r="C67" t="s">
+        <v>517</v>
+      </c>
+      <c r="D67" t="s">
+        <v>190</v>
+      </c>
+      <c r="E67" t="s">
+        <v>518</v>
+      </c>
+      <c r="F67" t="s">
+        <v>247</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>520</v>
+      </c>
+      <c r="B68" t="s">
+        <v>256</v>
+      </c>
+      <c r="C68" t="s">
+        <v>203</v>
+      </c>
+      <c r="D68" t="s">
+        <v>190</v>
+      </c>
+      <c r="E68" t="s">
+        <v>521</v>
+      </c>
+      <c r="F68" t="s">
+        <v>522</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>524</v>
+      </c>
+      <c r="B69" t="s">
+        <v>525</v>
+      </c>
+      <c r="C69" t="s">
+        <v>225</v>
+      </c>
+      <c r="D69" t="s">
+        <v>197</v>
+      </c>
+      <c r="E69" t="s">
+        <v>526</v>
+      </c>
+      <c r="F69" t="s">
+        <v>527</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>529</v>
+      </c>
+      <c r="B70" t="s">
+        <v>530</v>
+      </c>
+      <c r="C70" t="s">
+        <v>196</v>
+      </c>
+      <c r="D70" t="s">
+        <v>372</v>
+      </c>
+      <c r="E70" t="s">
+        <v>518</v>
+      </c>
+      <c r="F70" t="s">
+        <v>531</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>533</v>
+      </c>
+      <c r="B71" t="s">
+        <v>534</v>
+      </c>
+      <c r="C71" t="s">
+        <v>535</v>
+      </c>
+      <c r="D71" t="s">
+        <v>190</v>
+      </c>
+      <c r="E71" t="s">
+        <v>536</v>
+      </c>
+      <c r="F71" t="s">
+        <v>457</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>538</v>
+      </c>
+      <c r="B72" t="s">
+        <v>534</v>
+      </c>
+      <c r="C72" t="s">
+        <v>535</v>
+      </c>
+      <c r="D72" t="s">
+        <v>190</v>
+      </c>
+      <c r="E72" t="s">
+        <v>539</v>
+      </c>
+      <c r="F72" t="s">
+        <v>457</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>541</v>
+      </c>
+      <c r="B73" t="s">
+        <v>542</v>
+      </c>
+      <c r="C73" t="s">
+        <v>278</v>
+      </c>
+      <c r="D73" t="s">
+        <v>190</v>
+      </c>
+      <c r="E73" t="s">
+        <v>543</v>
+      </c>
+      <c r="F73" t="s">
+        <v>544</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>546</v>
+      </c>
+      <c r="B74" t="s">
+        <v>547</v>
+      </c>
+      <c r="C74" t="s">
+        <v>407</v>
+      </c>
+      <c r="D74" t="s">
+        <v>190</v>
+      </c>
+      <c r="E74" t="s">
+        <v>548</v>
+      </c>
+      <c r="F74" t="s">
+        <v>549</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>551</v>
+      </c>
+      <c r="B75" t="s">
+        <v>552</v>
+      </c>
+      <c r="C75" t="s">
+        <v>553</v>
+      </c>
+      <c r="D75" t="s">
+        <v>190</v>
+      </c>
+      <c r="E75" t="s">
+        <v>480</v>
+      </c>
+      <c r="F75" t="s">
+        <v>211</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>555</v>
+      </c>
+      <c r="B76" t="s">
+        <v>512</v>
+      </c>
+      <c r="C76" t="s">
+        <v>189</v>
+      </c>
+      <c r="D76" t="s">
+        <v>190</v>
+      </c>
+      <c r="E76" t="s">
+        <v>556</v>
+      </c>
+      <c r="F76" t="s">
+        <v>514</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>558</v>
+      </c>
+      <c r="B77" t="s">
+        <v>559</v>
+      </c>
+      <c r="C77" t="s">
+        <v>196</v>
+      </c>
+      <c r="D77" t="s">
+        <v>190</v>
+      </c>
+      <c r="E77" t="s">
+        <v>560</v>
+      </c>
+      <c r="F77" t="s">
+        <v>561</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>563</v>
+      </c>
+      <c r="B78" t="s">
+        <v>564</v>
+      </c>
+      <c r="C78" t="s">
+        <v>565</v>
+      </c>
+      <c r="D78" t="s">
+        <v>566</v>
+      </c>
+      <c r="E78" t="s">
+        <v>567</v>
+      </c>
+      <c r="F78" t="s">
+        <v>568</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>563</v>
+      </c>
+      <c r="B79" t="s">
+        <v>564</v>
+      </c>
+      <c r="C79" t="s">
+        <v>570</v>
+      </c>
+      <c r="D79" t="s">
+        <v>566</v>
+      </c>
+      <c r="E79" t="s">
+        <v>571</v>
+      </c>
+      <c r="F79" t="s">
+        <v>568</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>573</v>
+      </c>
+      <c r="B80" t="s">
+        <v>244</v>
+      </c>
+      <c r="C80" t="s">
+        <v>517</v>
+      </c>
+      <c r="D80" t="s">
+        <v>190</v>
+      </c>
+      <c r="E80" t="s">
+        <v>574</v>
+      </c>
+      <c r="F80" t="s">
+        <v>247</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>576</v>
+      </c>
+      <c r="B81" t="s">
+        <v>577</v>
+      </c>
+      <c r="C81" t="s">
+        <v>196</v>
+      </c>
+      <c r="D81" t="s">
+        <v>190</v>
+      </c>
+      <c r="E81" t="s">
+        <v>578</v>
+      </c>
+      <c r="F81" t="s">
+        <v>579</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>581</v>
+      </c>
+      <c r="B82" t="s">
+        <v>512</v>
+      </c>
+      <c r="C82" t="s">
+        <v>189</v>
+      </c>
+      <c r="D82" t="s">
+        <v>190</v>
+      </c>
+      <c r="E82" t="s">
+        <v>582</v>
+      </c>
+      <c r="F82" t="s">
+        <v>514</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>584</v>
+      </c>
+      <c r="B83" t="s">
+        <v>426</v>
+      </c>
+      <c r="C83" t="s">
+        <v>427</v>
+      </c>
+      <c r="D83" t="s">
+        <v>197</v>
+      </c>
+      <c r="E83" t="s">
+        <v>585</v>
+      </c>
+      <c r="F83" t="s">
+        <v>429</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>587</v>
+      </c>
+      <c r="B84" t="s">
+        <v>588</v>
+      </c>
+      <c r="C84" t="s">
+        <v>278</v>
+      </c>
+      <c r="D84" t="s">
+        <v>566</v>
+      </c>
+      <c r="E84" t="s">
+        <v>589</v>
+      </c>
+      <c r="F84" t="s">
+        <v>590</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-25.xlsx
+++ b/docs/xlsx/jobs-2026-09-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="837">
   <si>
     <t>Title</t>
   </si>
@@ -598,6 +598,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/0b41f3e5044b4051be3e0f2524050ac4-accountant-human-rights-watch-new-york</t>
   </si>
   <si>
+    <t>Administrative &amp; Executive Assistant — Part-Time</t>
+  </si>
+  <si>
+    <t>Impact Teen Drivers</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b27cac724b2f4d2cb648d121525a3198-administrative-executive-assistant-part-time-impact-teen-drivers-sacramento</t>
+  </si>
+  <si>
     <t>Administrative Assistant</t>
   </si>
   <si>
@@ -607,9 +628,6 @@
     <t>Remote</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 25.10/hour</t>
   </si>
   <si>
@@ -637,6 +655,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/6a8c2744a91c4ee4ba162b139f8af72e-admissions-manager-mattapan-residential-casual-boston-public-health-commission-boston</t>
   </si>
   <si>
+    <t>Advocacy Manager - CAA</t>
+  </si>
+  <si>
+    <t>Asian Americans for Civil Rights and Equality (AACRE)</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 103438.00 - 108000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aed510622425428ba7159e17604b1596-advocacy-manager-caa-asian-americans-for-civil-rights-and-equality-aacre-san-francisco</t>
+  </si>
+  <si>
     <t>Agente en vía pública | CABA y GBA</t>
   </si>
   <si>
@@ -670,6 +706,36 @@
     <t>https://www.idealist.org/en/government-job/87786b89c81a4c559d0e951160c2b390-assistant-attorney-general-office-of-the-massachusetts-attorney-general-boston</t>
   </si>
   <si>
+    <t>Assistant to the Director</t>
+  </si>
+  <si>
+    <t>Posse Foundation, Miami</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 42000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a330b421e3f4be693ecfd10d2e3ccae-assistant-to-the-director-posse-foundation-miami-miami</t>
+  </si>
+  <si>
+    <t>Associate Director of Advancement</t>
+  </si>
+  <si>
+    <t>Institute for Shipboard Education/Semester at Sea</t>
+  </si>
+  <si>
+    <t>USD 76000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0696d64c621543eab98ccdf645d9de5b-associate-director-of-advancement-institute-for-shipboard-educationsemester-at-sea-fort-collins</t>
+  </si>
+  <si>
     <t>Associate Director Seattle, Washington</t>
   </si>
   <si>
@@ -745,6 +811,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/737b4fbebe9f435c8c8b765ad6da36b4-brooklyn-director-of-development-jeremiah-programminneapolis-new-york</t>
   </si>
   <si>
+    <t>Campaign Communicator and Digital Specialist</t>
+  </si>
+  <si>
+    <t>The Action Lab</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 55.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e692469001743bfa5a945f3b18db555-campaign-communicator-and-digital-specialist-the-action-lab-new-york</t>
+  </si>
+  <si>
     <t>Case Manager</t>
   </si>
   <si>
@@ -763,6 +847,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/c4b2f979995a4e2697375e0e071e4a9b-case-manager-springwell-inc-marlborough</t>
   </si>
   <si>
+    <t>Case Manager (Supported Living Disability Services)</t>
+  </si>
+  <si>
+    <t>Toolworks</t>
+  </si>
+  <si>
+    <t>USD 73819.00 - 75592.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6575b02e35114d0b9b7afa2bd76f57a3-case-manager-supported-living-disability-services-toolworks-san-francisco</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>The Arc of Prince George's County</t>
+  </si>
+  <si>
+    <t>Largo, Maryland</t>
+  </si>
+  <si>
+    <t>USD 200000.00 - 215000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/46201cc1f1f24fd3bfa9ccc78b3462a2-chief-financial-officer-the-arc-of-prince-georges-county-largo</t>
+  </si>
+  <si>
     <t>Chief Marketing Officer</t>
   </si>
   <si>
@@ -781,6 +895,57 @@
     <t>https://www.idealist.org/en/job/ac881ec560064737bd7b7646e2b51a4a-chief-marketing-officer-leadership-greater-chicago-chicago</t>
   </si>
   <si>
+    <t>Chief Program Officer</t>
+  </si>
+  <si>
+    <t>Future Caucus</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 151000.00 - 163000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/284230fadded46a2a67671a28909793e-chief-program-officer-future-caucus-washington</t>
+  </si>
+  <si>
+    <t>Clean Air Advocate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>USD 41750.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/06da7b14dfd94637a5f9c79d2af22d7e-clean-air-advocate-environment-america-boston</t>
+  </si>
+  <si>
+    <t>Clinical Nurse II, CS-0610-09</t>
+  </si>
+  <si>
+    <t>District of Columbia Department of Youth Rehabilitation Services</t>
+  </si>
+  <si>
+    <t>Laurel, Maryland</t>
+  </si>
+  <si>
+    <t>USD 87865.00 - 115907.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/9c3a0cf72c694d30a52d37c99851342b-clinical-nurse-ii-cs-0610-09-district-of-columbia-department-of-youth-rehabilitation-services-laurel</t>
+  </si>
+  <si>
     <t>Clinical Supervisor - LaGrange</t>
   </si>
   <si>
@@ -826,6 +991,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/94645c83bcc14d0ca89dd6e3098bc2f4-community-advocacy-specialist-brookview-house-inc-boston</t>
   </si>
   <si>
+    <t>Community Coach I (Full-Time) [Mon-Fri (9AM-6PM)] [LLFrank]</t>
+  </si>
+  <si>
+    <t>AbilityFirst</t>
+  </si>
+  <si>
+    <t>Pasadena, California</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/d0f3a700b80242259bd43f1e2e678eef-community-coach-i-full-time-mon-fri-9am-6pm-llfrank-abilityfirst-pasadena</t>
+  </si>
+  <si>
+    <t>Community Coach I (Part-Time) [Monday – Friday (8am-1pm)]</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ba5247ccb8a44724afb2d2d0d3e14ac7-community-coach-i-part-time-monday-friday-8am-1pm-abilityfirst-pasadena</t>
+  </si>
+  <si>
     <t>Community Education Intern</t>
   </si>
   <si>
@@ -838,21 +1024,81 @@
     <t>https://www.idealist.org/en/job/5e597a3507ce49a5bb070b0369ebd0e6-community-education-intern-nyc-campaign-finance-board-new-york</t>
   </si>
   <si>
+    <t>Community Engagement &amp; Education Coordinator</t>
+  </si>
+  <si>
+    <t>The Mizel Institute</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/32f5694a8f694bf3aa21175cd2bac771-community-engagement-education-coordinator-the-mizel-institute-denver</t>
+  </si>
+  <si>
+    <t>Community Engagement Coordinator Assistant New Britain</t>
+  </si>
+  <si>
+    <t>Leaders for Educational Advocacy and Diversity (LEAD)</t>
+  </si>
+  <si>
+    <t>New Britain, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d51b1b5cd53e4a398f4e0bb07976bcb2-community-engagement-coordinator-assistant-new-britain-leaders-for-educational-advocacy-and-diversity-lead-new-britain</t>
+  </si>
+  <si>
+    <t>Community Experience Representative</t>
+  </si>
+  <si>
+    <t>Yerba Buena Center for the Arts</t>
+  </si>
+  <si>
+    <t>San Francisco, CA</t>
+  </si>
+  <si>
+    <t>USD 27.81 - 27.81/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b08c76c2ce8240c488bd000cafeb743e-community-experience-representative-yerba-buena-center-for-the-arts-san-francisco</t>
+  </si>
+  <si>
     <t>Community Outreach Intern</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/job/8e5055962c2648409e897d02bc5b0d78-community-outreach-intern-nyc-campaign-finance-board-new-york</t>
   </si>
   <si>
+    <t>Conservation Advocate</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba3caf363b7c4d7981028b13c8c6339c-conservation-advocate-environment-america-madison</t>
+  </si>
+  <si>
     <t>Controller</t>
   </si>
   <si>
     <t>PaintCare &amp; American Coatings Association</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 165000.00 - 175000.00/year</t>
   </si>
   <si>
@@ -916,9 +1162,6 @@
     <t>International Rescue Committee - Sacramento</t>
   </si>
   <si>
-    <t>Sacramento, California</t>
-  </si>
-  <si>
     <t>USD 109416.00 - 109416.00/year</t>
   </si>
   <si>
@@ -928,6 +1171,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/45e9c313f5c74822a99e799b2b47f23c-development-director-international-rescue-committee-sacramento-sacramento</t>
   </si>
   <si>
+    <t>Development Operations and Grant Administrator</t>
+  </si>
+  <si>
+    <t>Girls Inc. of Long Island</t>
+  </si>
+  <si>
+    <t>Deer Park, NY</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45a4f448f5ce4868b892cba6fa03302a-development-operations-and-grant-administrator-girls-inc-of-long-island-deer-park</t>
+  </si>
+  <si>
     <t>Director of Budget and Analysis</t>
   </si>
   <si>
@@ -994,6 +1255,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/e3127125ed4948c88fd29a99b668c944-director-of-development-transportation-alternatives-new-york</t>
   </si>
   <si>
+    <t>Parks &amp; People, Inc.</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0fb7a71ac8ee480c860f2f9497191c68-director-of-development-parks-people-inc-baltimore</t>
+  </si>
+  <si>
     <t>Director of Email and SMS Campaigns</t>
   </si>
   <si>
@@ -1009,6 +1285,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/de1bffe8c81c41388eebf96cacf64433-director-of-email-and-sms-campaigns-everytown-for-gun-safety-new-york</t>
   </si>
   <si>
+    <t>Director of Events</t>
+  </si>
+  <si>
+    <t>The Phillips Collection</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b826aead38f417c8ac89ee9d08ee451-director-of-events-the-phillips-collection-washington</t>
+  </si>
+  <si>
+    <t>Director of Finance and Administration</t>
+  </si>
+  <si>
+    <t>Project Adventure, Inc.</t>
+  </si>
+  <si>
+    <t>Beverly, MA</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Mental Health, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa8efe41abd24259b1cde4a9e86312ef-director-of-finance-and-administration-project-adventure-inc-beverly</t>
+  </si>
+  <si>
     <t>Director of People Operations</t>
   </si>
   <si>
@@ -1024,6 +1333,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/a8fa8c71dc804cdca0dd3038469a7f6b-director-of-people-operations-center-for-civic-design-cambridge</t>
   </si>
   <si>
+    <t>Director of Programs, On The Rise</t>
+  </si>
+  <si>
+    <t>Eos Transition Partners</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Crime Safety, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/100f9139771c4b6c89f4d68b7ba2fe3e-director-of-programs-on-the-rise-eos-transition-partners-cambridge</t>
+  </si>
+  <si>
     <t>Director of Social Services</t>
   </si>
   <si>
@@ -1051,6 +1378,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/199b8bee8e2d447d8640fb94ff9d5b9a-director-clearinghouse-services-health-resources-in-action-inc-boston</t>
   </si>
   <si>
+    <t>Director, Federal Campaigns</t>
+  </si>
+  <si>
+    <t>USD 43500.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d438187d68ed40c784da10b3dd8ddb59-director-federal-campaigns-environment-america-washington</t>
+  </si>
+  <si>
     <t>Director, Marketing and Communication</t>
   </si>
   <si>
@@ -1078,6 +1417,93 @@
     <t>https://www.idealist.org/en/nonprofit-job/6467a3fca57e47fd85f1ff5819ac50c9-director-marketing-strategy-the-jewish-federation-of-greater-washington-n-bethesda</t>
   </si>
   <si>
+    <t>DSP Supported and Independent Living Instructor</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de6ade07734c4e7ba4743aac04e45851-dsp-supported-and-independent-living-instructor-toolworks-san-francisco</t>
+  </si>
+  <si>
+    <t>DSP Supported and Independent Living Lead</t>
+  </si>
+  <si>
+    <t>USD 29.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75f21d566df944448c93fe2df9a3d856-dsp-supported-and-independent-living-lead-toolworks-san-francisco</t>
+  </si>
+  <si>
+    <t>Education &amp; Event Coordinator</t>
+  </si>
+  <si>
+    <t>Project Chimps</t>
+  </si>
+  <si>
+    <t>Morganton, Georgia</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Animals, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac1c267df27846cfb05422e2c5337cf8-education-event-coordinator-project-chimps-morganton</t>
+  </si>
+  <si>
+    <t>Education Outreach Manager — California</t>
+  </si>
+  <si>
+    <t>San Jose, California</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/92182721c7c84b06897e07405ce34c4c-education-outreach-manager-california-impact-teen-drivers-san-jose</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c33adf9cacc47e9ba40e726a813ccdb-education-outreach-manager-california-impact-teen-drivers-sacramento</t>
+  </si>
+  <si>
+    <t>Education Outreach Manager 1 — California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05d55c7bcaf940d8a72c10ed41154a9c-education-outreach-manager-1-california-impact-teen-drivers-san-francisco</t>
+  </si>
+  <si>
+    <t>Executive Assitant</t>
+  </si>
+  <si>
+    <t>Friends of the Amargosa Basin</t>
+  </si>
+  <si>
+    <t>Shoshone, California</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Rural Areas, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d98d6de3fff4c1c846c54b6dc8b3048-executive-assitant-friends-of-the-amargosa-basin-shoshone</t>
+  </si>
+  <si>
+    <t>Executive Coordinator, Development and External Affair</t>
+  </si>
+  <si>
+    <t>Third Way</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5965780445342cdbdb97d361d6ff723-executive-coordinator-development-and-external-affair-third-way-washington</t>
+  </si>
+  <si>
     <t>Coastal Neighbors</t>
   </si>
   <si>
@@ -1093,6 +1519,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/c4ae31feb6c84688b66f160f0420de8e-executive-director-coastal-neighbors-dartmouth</t>
   </si>
   <si>
+    <t>Access Opportunity</t>
+  </si>
+  <si>
+    <t>Boulder, Colorado</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1c71b148330d47f590438e2443f11549-executive-director-access-opportunity-boulder</t>
+  </si>
+  <si>
     <t>Executive Director, Dress for Success Greater New York City</t>
   </si>
   <si>
@@ -1144,6 +1579,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/fb9f4d565c27423b9aef1849853bc378-facilitadora-educativoa-en-cdmx-edo-mex-presencial-educacion-para-compartir-mexico-ciudad-de-mexico</t>
   </si>
   <si>
+    <t>Federal Legislative Associate</t>
+  </si>
+  <si>
+    <t>U.S. PIRG</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Transparency Oversight, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3533a3c190fb4e6daf263be4cd63bf3a-federal-legislative-associate-us-pirg-washington</t>
+  </si>
+  <si>
     <t>Foster Care Licensing and Placement Specialist</t>
   </si>
   <si>
@@ -1192,9 +1642,6 @@
     <t>Ossining, NY</t>
   </si>
   <si>
-    <t>USD 50000.00 - 60000.00/year</t>
-  </si>
-  <si>
     <t>Civic Engagement, Climate Change, Community Development</t>
   </si>
   <si>
@@ -1216,6 +1663,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/1315218897ec42ee96a9844861ca98f4-health-counselor-cssny-new-york</t>
   </si>
   <si>
+    <t>Healthcare Campaign Associate</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Consumer Protection, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/713cde3bb57d446083cb70d0c7656caa-healthcare-campaign-associate-us-pirg-portland</t>
+  </si>
+  <si>
+    <t>HICAP Medicare Advocate I</t>
+  </si>
+  <si>
+    <t>Legal Assistance for Seniors</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 27.22 - 27.22/hour</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Consumer Protection, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bbffc57bef964a778f12b9158cabae5a-hicap-medicare-advocate-i-legal-assistance-for-seniors-oakland</t>
+  </si>
+  <si>
     <t>HR Worker Care Manager</t>
   </si>
   <si>
@@ -1345,9 +1819,6 @@
     <t>Reproductive Freedom for All</t>
   </si>
   <si>
-    <t>San Francisco, California</t>
-  </si>
-  <si>
     <t>USD 75000.00 - 125000.00/year</t>
   </si>
   <si>
@@ -1357,6 +1828,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/30884d5ca1084ae5b510b97e9b018546-major-gifts-officer-reproductive-freedom-for-all-san-francisco</t>
   </si>
   <si>
+    <t>Manager of Billing Operations</t>
+  </si>
+  <si>
+    <t>Scale to Win</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/6a740864dcbc411e81d38628b6582ae7-manager-of-billing-operations-scale-to-win-santa-ana</t>
+  </si>
+  <si>
     <t>Manager of Intergenerational Programs</t>
   </si>
   <si>
@@ -1372,6 +1855,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/957ab7c5401845abae0730d408bc6c42-manager-of-intergenerational-programs-openhouse-san-francisco</t>
   </si>
   <si>
+    <t>Managing Attorney (Children's Appellate Advocacy &amp; Complex Litigation)</t>
+  </si>
+  <si>
+    <t>Immigrant Defenders Law Center</t>
+  </si>
+  <si>
+    <t>USD 91000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/69614c1e00d647b1a1133aa3ca645934-managing-attorney-childrens-appellate-advocacy-complex-litigation-immigrant-defenders-law-center-los-angeles</t>
+  </si>
+  <si>
+    <t>Managing Attorney (Immigration Removal Defense - Children)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a104bec92aac460ea24c7378a8ad79da-managing-attorney-immigration-removal-defense-children-immigrant-defenders-law-center-los-angeles</t>
+  </si>
+  <si>
     <t>Managing Director</t>
   </si>
   <si>
@@ -1381,6 +1885,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/58832529cb2b43ffb776b9323d6a1254-managing-director-transportation-alternatives-new-york</t>
   </si>
   <si>
+    <t>Mental Health Program Manager</t>
+  </si>
+  <si>
+    <t>CIC for Prevention and Recovery</t>
+  </si>
+  <si>
+    <t>Bernardsville, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 60000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5ff98f0a9144481f9cafd15925a1027b-mental-health-program-manager-cic-for-prevention-and-recovery-bernardsville</t>
+  </si>
+  <si>
     <t>Mentoring Case Manager</t>
   </si>
   <si>
@@ -1408,6 +1930,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/113c9c1ef7b841e6934b5a55af5dca9b-middle-school-after-school-site-director-manhattan-youth-recreation-and-resources-inc-new-york</t>
   </si>
   <si>
+    <t>Monitoring, Evaluation, and Learning Officer</t>
+  </si>
+  <si>
+    <t>Notify Health</t>
+  </si>
+  <si>
+    <t>Remote (NG)</t>
+  </si>
+  <si>
+    <t>NGN 500000.00 - 730000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2dca07b35cd74a96951e58065c911eb9-monitoring-evaluation-and-learning-officer-notify-health-london</t>
+  </si>
+  <si>
+    <t>New Hampshire Conservation Advocate</t>
+  </si>
+  <si>
+    <t>Manchester, New Hampshire</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b453b929f8e42f99312fd3a4864ef6f-new-hampshire-conservation-advocate-environment-america-manchester</t>
+  </si>
+  <si>
     <t>Office and Events Manager</t>
   </si>
   <si>
@@ -1417,6 +1966,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/ee6fbbddd19046fc87194a224fc810ad-office-and-events-manager-asia-society-washington</t>
   </si>
   <si>
+    <t>Office Manager</t>
+  </si>
+  <si>
+    <t>Perfectly Flawed Foundation</t>
+  </si>
+  <si>
+    <t>La Salle, Illinois</t>
+  </si>
+  <si>
+    <t>USD 38000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/870ab42deec84b00b49b60f3138ae123-office-manager-perfectly-flawed-foundation-la-salle</t>
+  </si>
+  <si>
     <t>Operations &amp; Development Consultant (Independent Contractor, Remote)</t>
   </si>
   <si>
@@ -1465,6 +2029,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/d526842f5ace460a87a68e06b157775b-operations-specialist-caringkind-your-trusted-partner-in-alzheimers-and-dementia-care-new-york</t>
   </si>
   <si>
+    <t>Part Time Director of Enrichment Program</t>
+  </si>
+  <si>
+    <t>Oddfellows Playhouse</t>
+  </si>
+  <si>
+    <t>Middletown, Connecticut</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/64c01a90f4e34f5dad7881674657e9a1-part-time-director-of-enrichment-program-oddfellows-playhouse-middletown</t>
+  </si>
+  <si>
     <t>Part-time ESL Instructor</t>
   </si>
   <si>
@@ -1480,6 +2059,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/1631192f072844c18c571dbe75121ef5-part-time-esl-instructor-arab-american-association-of-new-york-kings-county</t>
   </si>
   <si>
+    <t>Partnership Coordinator</t>
+  </si>
+  <si>
+    <t>The Campaign for College Opportunity</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/74b1489165474f388c3bf108f3fcd6f7-partnership-coordinator-the-campaign-for-college-opportunity-los-angeles</t>
+  </si>
+  <si>
+    <t>Plastic Pellet Free Waters Campaign Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/92f2b5efac8e4626b6fa8da2242d051c-plastic-pellet-free-waters-campaign-associate-environment-america-portland</t>
+  </si>
+  <si>
     <t>Preschool Teacher ($500 Sign on Bonus)</t>
   </si>
   <si>
@@ -1507,15 +2107,24 @@
     <t>Pawtucket, Rhode Island</t>
   </si>
   <si>
-    <t>USD 20.00 - 22.00/hour</t>
-  </si>
-  <si>
-    <t>Children Youth, Civic Engagement, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/e9cb394f732d40e482904b004f051d18-program-and-outreach-coordinator-books-are-wings-pawtucket</t>
   </si>
   <si>
+    <t>Program Coordinator, Clinical Law Center</t>
+  </si>
+  <si>
+    <t>Howard University School of Law</t>
+  </si>
+  <si>
+    <t>USD 57500.00 - 67500.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Education, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75d086707ca3401db1ec6ddbb4f42103-program-coordinator-clinical-law-center-howard-university-school-of-law-washington</t>
+  </si>
+  <si>
     <t>Program Manager</t>
   </si>
   <si>
@@ -1549,6 +2158,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/5cf5181c183d49ae8f448cc785979571-program-manager-india-uttar-pradesh-lead-exposure-elimination-project-london</t>
   </si>
   <si>
+    <t>Program Specialist, Boston - 30hrs/week - Hybrid</t>
+  </si>
+  <si>
+    <t>Literations</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 59000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ab11768ed56b4ce4ad2acc9cec23133b-program-specialist-boston-30hrsweek-hybrid-literations-boston</t>
+  </si>
+  <si>
+    <t>Proposal Development Manager</t>
+  </si>
+  <si>
+    <t>Alford Group</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/0977d817e70d4183899cecc50912f39c-proposal-development-manager-alford-group-chicago</t>
+  </si>
+  <si>
     <t>Rapid Response Paralegal</t>
   </si>
   <si>
@@ -1570,9 +2206,6 @@
     <t>Waltham, Massachusetts</t>
   </si>
   <si>
-    <t>USD 80000.00 - 80000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/72ac41fb1e664e4baae6dec942aeb2a5-registered-nurse-rn-springwell-inc-waltham</t>
   </si>
   <si>
@@ -1597,9 +2230,6 @@
     <t>USD 20.00 - 24.00/hour</t>
   </si>
   <si>
-    <t>Children Youth, Community Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/2a4d115c4caa46ed93696d2748a0863e-school-based-mentoring-program-program-specialist-big-brothers-big-sisters-of-greater-los-angeles-los-angeles</t>
   </si>
   <si>
@@ -1615,6 +2245,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/45dc48c85db84746a42e84172eb2ea39-senior-data-engineer-tech-equity-fellowship-code-the-dream-durham</t>
   </si>
   <si>
+    <t>Senior Development Manager/Development Manager (Title &amp; Level Determined by Experience &amp; Qualifications)</t>
+  </si>
+  <si>
+    <t>Children &amp; Nature Network</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Environment, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c566eb08a7e242148152c087c9fafbf5-senior-development-managerdevelopment-manager-title-level-determined-by-experience-qualifications-children-nature-network-roseville</t>
+  </si>
+  <si>
+    <t>Senior Digital Media Advisor</t>
+  </si>
+  <si>
+    <t>USD 84000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Media, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b810ddd5d7f2421698b384cb4facda15-senior-digital-media-advisor-third-way-washington</t>
+  </si>
+  <si>
     <t>Senior Director of Family and Community Programs</t>
   </si>
   <si>
@@ -1639,6 +2296,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/7c92e415494d4b2bbeb1f74cb206002c-senior-director-of-people-and-culture-family-nurturing-center-of-ma-dorchester</t>
   </si>
   <si>
+    <t>Senior Director, Finance</t>
+  </si>
+  <si>
+    <t>USD 101500.00 - 109600.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ed96e4f6f504b02a5e7f09864f0d107-senior-director-finance-future-caucus-washington</t>
+  </si>
+  <si>
+    <t>Senior Manager, Individual Giving</t>
+  </si>
+  <si>
+    <t>Animal Care Centers of NYC</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a93de82fd6f74b2ab1675291b3f49896-senior-manager-individual-giving-animal-care-centers-of-nyc-new-york</t>
+  </si>
+  <si>
     <t>Senior Policy Analyst, Health Policy</t>
   </si>
   <si>
@@ -1690,6 +2368,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/7516948e35f94881a6dadb4d5b49c5e3-staff-attorney-new-york-legal-assistance-group-nylag-new-york</t>
   </si>
   <si>
+    <t>Staff Attorney (Crimmigration Specialist / Public Defender Partnership)</t>
+  </si>
+  <si>
+    <t>USD 82000.00 - 97000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/03e6f25a30b845288c01194a5015c16c-staff-attorney-crimmigration-specialist-public-defender-partnership-immigrant-defenders-law-center-los-angeles</t>
+  </si>
+  <si>
+    <t>Staff Attorney (Immigration Removal Defense)</t>
+  </si>
+  <si>
+    <t>San Diego, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e110e116ea2e44fb8f7589cb2827f33d-staff-attorney-immigration-removal-defense-immigrant-defenders-law-center-san-diego</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6554a936f4464fba93004dc7cb2c93d7-staff-attorney-immigration-removal-defense-immigrant-defenders-law-center-los-angeles</t>
+  </si>
+  <si>
+    <t>Riverside, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e877f86827e34f9183f8262e8d0a8f99-staff-attorney-immigration-removal-defense-immigrant-defenders-law-center-riverside</t>
+  </si>
+  <si>
     <t>Staff or Sr. Staff Attorney - Child and Youth Rights Facilities and Community</t>
   </si>
   <si>
@@ -1714,9 +2419,6 @@
     <t>Remote (Allentown, Pennsylvania)</t>
   </si>
   <si>
-    <t>Part Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 25.00 - 25.00/hour</t>
   </si>
   <si>
@@ -1729,12 +2431,21 @@
     <t>Remote (New York)</t>
   </si>
   <si>
-    <t>USD 27.00 - 27.00/hour</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/2d720c33a3754ea9aaac2695c5fd7e73-stop-data-centers-canvasser-food-water-watch-yonkers</t>
   </si>
   <si>
+    <t>Substitute Tutor</t>
+  </si>
+  <si>
+    <t>Southeast Community Foundation</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 31.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/98f52cfb5db74ad9869dba6f33ccb5ad-substitute-tutor-southeast-community-foundation-los-angeles</t>
+  </si>
+  <si>
     <t>Supervisor</t>
   </si>
   <si>
@@ -1777,6 +2488,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/a3ada64004bf46f897cd865166549fec-upward-mentoring-manager-part-time-big-brothers-big-sisters-of-eastern-missouri-st-louis</t>
   </si>
   <si>
+    <t>Volunteer &amp; Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>Berkeley Food Network</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/686df62f5d59463295b195517fc318d0-volunteer-outreach-coordinator-berkeley-food-network-berkeley</t>
+  </si>
+  <si>
     <t>Youth Program Assistant Instructor</t>
   </si>
   <si>
@@ -1790,6 +2519,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/0859c2e919d5490282a07662dad974ed-youth-program-assistant-instructor-many-languages-one-voice-washington</t>
+  </si>
+  <si>
+    <t>Zero Waste Advocate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a05da88861704802abcac8c1fce6c5a2-zero-waste-advocate-us-pirg-denver</t>
   </si>
 </sst>
 </file>
@@ -3089,7 +3824,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H142"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3208,27 +3943,27 @@
         <v>209</v>
       </c>
       <c r="D5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E5" t="s">
         <v>210</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>211</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" t="s">
         <v>214</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>215</v>
-      </c>
-      <c r="C6" t="s">
-        <v>203</v>
       </c>
       <c r="D6" t="s">
         <v>190</v>
@@ -3237,159 +3972,159 @@
         <v>216</v>
       </c>
       <c r="F6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D7" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="E7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B8" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="C8" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D8" t="s">
         <v>190</v>
       </c>
       <c r="E8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F8" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C9" t="s">
-        <v>189</v>
+        <v>232</v>
       </c>
       <c r="D9" t="s">
         <v>190</v>
       </c>
       <c r="E9" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" t="s">
+        <v>203</v>
+      </c>
+      <c r="D10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F10" t="s">
         <v>234</v>
       </c>
-      <c r="C10" t="s">
-        <v>235</v>
-      </c>
-      <c r="D10" t="s">
-        <v>190</v>
-      </c>
-      <c r="E10" t="s">
-        <v>211</v>
-      </c>
-      <c r="F10" t="s">
-        <v>236</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C11" t="s">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="D11" t="s">
         <v>190</v>
       </c>
       <c r="E11" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F11" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B12" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D12" t="s">
         <v>190</v>
       </c>
       <c r="E12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F12" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C13" t="s">
-        <v>251</v>
+        <v>189</v>
       </c>
       <c r="D13" t="s">
         <v>190</v>
@@ -3412,13 +4147,13 @@
         <v>256</v>
       </c>
       <c r="C14" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="D14" t="s">
         <v>190</v>
       </c>
       <c r="E14" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="F14" t="s">
         <v>258</v>
@@ -3435,7 +4170,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D15" t="s">
         <v>190</v>
@@ -3458,283 +4193,283 @@
         <v>266</v>
       </c>
       <c r="C16" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="E16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>273</v>
       </c>
       <c r="D17" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E17" t="s">
-        <v>211</v>
+        <v>274</v>
       </c>
       <c r="F17" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B18" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C18" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D18" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E18" t="s">
-        <v>211</v>
+        <v>279</v>
       </c>
       <c r="F18" t="s">
-        <v>272</v>
+        <v>223</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B19" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C19" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D19" t="s">
         <v>190</v>
       </c>
       <c r="E19" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F19" t="s">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B20" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C20" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D20" t="s">
         <v>190</v>
       </c>
       <c r="E20" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F20" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B21" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C21" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="D21" t="s">
         <v>190</v>
       </c>
       <c r="E21" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F21" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B22" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C22" t="s">
-        <v>295</v>
+        <v>209</v>
       </c>
       <c r="D22" t="s">
         <v>190</v>
       </c>
       <c r="E22" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F22" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B23" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C23" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D23" t="s">
         <v>190</v>
       </c>
       <c r="E23" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F23" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B24" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C24" t="s">
-        <v>306</v>
+        <v>209</v>
       </c>
       <c r="D24" t="s">
         <v>190</v>
       </c>
       <c r="E24" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F24" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B25" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C25" t="s">
-        <v>312</v>
+        <v>203</v>
       </c>
       <c r="D25" t="s">
         <v>190</v>
       </c>
       <c r="E25" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="F25" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B26" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C26" t="s">
-        <v>278</v>
+        <v>209</v>
       </c>
       <c r="D26" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E26" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F26" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B27" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C27" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D27" t="s">
         <v>190</v>
       </c>
       <c r="E27" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="F27" t="s">
-        <v>324</v>
+        <v>223</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>330</v>
+      </c>
+      <c r="B28" t="s">
         <v>326</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>327</v>
-      </c>
-      <c r="C28" t="s">
-        <v>189</v>
       </c>
       <c r="D28" t="s">
         <v>190</v>
@@ -3743,27 +4478,27 @@
         <v>328</v>
       </c>
       <c r="F28" t="s">
-        <v>329</v>
+        <v>223</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B29" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D29" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E29" t="s">
-        <v>333</v>
+        <v>223</v>
       </c>
       <c r="F29" t="s">
         <v>334</v>
@@ -3789,99 +4524,99 @@
         <v>339</v>
       </c>
       <c r="F30" t="s">
-        <v>211</v>
+        <v>340</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B31" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C31" t="s">
-        <v>203</v>
+        <v>344</v>
       </c>
       <c r="D31" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E31" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F31" t="s">
-        <v>211</v>
+        <v>346</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B32" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C32" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D32" t="s">
         <v>190</v>
       </c>
       <c r="E32" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F32" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B33" t="s">
-        <v>288</v>
+        <v>333</v>
       </c>
       <c r="C33" t="s">
-        <v>289</v>
+        <v>189</v>
       </c>
       <c r="D33" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E33" t="s">
-        <v>352</v>
+        <v>223</v>
       </c>
       <c r="F33" t="s">
-        <v>291</v>
+        <v>334</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>63</v>
+        <v>356</v>
       </c>
       <c r="B34" t="s">
-        <v>354</v>
+        <v>300</v>
       </c>
       <c r="C34" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D34" t="s">
         <v>190</v>
       </c>
       <c r="E34" t="s">
-        <v>356</v>
+        <v>301</v>
       </c>
       <c r="F34" t="s">
-        <v>357</v>
+        <v>302</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>358</v>
@@ -3895,7 +4630,7 @@
         <v>360</v>
       </c>
       <c r="C35" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="D35" t="s">
         <v>190</v>
@@ -3904,21 +4639,21 @@
         <v>361</v>
       </c>
       <c r="F35" t="s">
+        <v>223</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>363</v>
+      </c>
+      <c r="B36" t="s">
         <v>364</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>365</v>
-      </c>
-      <c r="C36" t="s">
-        <v>196</v>
       </c>
       <c r="D36" t="s">
         <v>190</v>
@@ -3944,36 +4679,36 @@
         <v>371</v>
       </c>
       <c r="D37" t="s">
+        <v>190</v>
+      </c>
+      <c r="E37" t="s">
         <v>372</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>373</v>
       </c>
-      <c r="F37" t="s">
+      <c r="H37" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>375</v>
+      </c>
+      <c r="B38" t="s">
         <v>376</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>377</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
+        <v>190</v>
+      </c>
+      <c r="E38" t="s">
         <v>378</v>
       </c>
-      <c r="D38" t="s">
-        <v>190</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>379</v>
-      </c>
-      <c r="F38" t="s">
-        <v>211</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>380</v>
@@ -3981,10 +4716,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>375</v>
+      </c>
+      <c r="B39" t="s">
         <v>381</v>
-      </c>
-      <c r="B39" t="s">
-        <v>382</v>
       </c>
       <c r="C39" t="s">
         <v>196</v>
@@ -3993,159 +4728,159 @@
         <v>190</v>
       </c>
       <c r="E39" t="s">
+        <v>382</v>
+      </c>
+      <c r="F39" t="s">
         <v>383</v>
       </c>
-      <c r="F39" t="s">
+      <c r="H39" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>385</v>
+      </c>
+      <c r="B40" t="s">
         <v>386</v>
       </c>
-      <c r="B40" t="s">
-        <v>244</v>
-      </c>
       <c r="C40" t="s">
-        <v>245</v>
+        <v>387</v>
       </c>
       <c r="D40" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E40" t="s">
-        <v>246</v>
+        <v>388</v>
       </c>
       <c r="F40" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B41" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C41" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D41" t="s">
         <v>190</v>
       </c>
       <c r="E41" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F41" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B42" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C42" t="s">
-        <v>189</v>
+        <v>399</v>
       </c>
       <c r="D42" t="s">
         <v>190</v>
       </c>
       <c r="E42" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="F42" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B43" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C43" t="s">
-        <v>196</v>
+        <v>295</v>
       </c>
       <c r="D43" t="s">
         <v>190</v>
       </c>
       <c r="E43" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F43" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B44" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C44" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D44" t="s">
         <v>190</v>
       </c>
       <c r="E44" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F44" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B45" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C45" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D45" t="s">
         <v>190</v>
       </c>
       <c r="E45" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F45" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B46" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C46" t="s">
         <v>189</v>
@@ -4154,309 +4889,309 @@
         <v>190</v>
       </c>
       <c r="E46" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F46" t="s">
-        <v>211</v>
+        <v>421</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B47" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C47" t="s">
-        <v>196</v>
+        <v>295</v>
       </c>
       <c r="D47" t="s">
         <v>190</v>
       </c>
       <c r="E47" t="s">
-        <v>211</v>
+        <v>425</v>
       </c>
       <c r="F47" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B48" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C48" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D48" t="s">
         <v>190</v>
       </c>
       <c r="E48" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F48" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B49" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C49" t="s">
-        <v>433</v>
+        <v>203</v>
       </c>
       <c r="D49" t="s">
         <v>190</v>
       </c>
       <c r="E49" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F49" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B50" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C50" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="D50" t="s">
         <v>190</v>
       </c>
       <c r="E50" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F50" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B51" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C51" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D51" t="s">
         <v>190</v>
       </c>
       <c r="E51" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F51" t="s">
-        <v>445</v>
+        <v>223</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B52" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C52" t="s">
-        <v>443</v>
+        <v>209</v>
       </c>
       <c r="D52" t="s">
         <v>190</v>
       </c>
       <c r="E52" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F52" t="s">
-        <v>450</v>
+        <v>223</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B53" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="C53" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="D53" t="s">
         <v>190</v>
       </c>
       <c r="E53" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F53" t="s">
-        <v>324</v>
+        <v>456</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B54" t="s">
-        <v>426</v>
+        <v>459</v>
       </c>
       <c r="C54" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D54" t="s">
         <v>190</v>
       </c>
       <c r="E54" t="s">
-        <v>428</v>
+        <v>461</v>
       </c>
       <c r="F54" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B55" t="s">
-        <v>460</v>
+        <v>370</v>
       </c>
       <c r="C55" t="s">
-        <v>189</v>
+        <v>371</v>
       </c>
       <c r="D55" t="s">
         <v>190</v>
       </c>
       <c r="E55" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F55" t="s">
-        <v>462</v>
+        <v>373</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B56" t="s">
-        <v>229</v>
+        <v>278</v>
       </c>
       <c r="C56" t="s">
-        <v>278</v>
+        <v>215</v>
       </c>
       <c r="D56" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E56" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F56" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B57" t="s">
-        <v>468</v>
+        <v>278</v>
       </c>
       <c r="C57" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D57" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="E57" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F57" t="s">
-        <v>470</v>
+        <v>223</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B58" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C58" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D58" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E58" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F58" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B59" t="s">
-        <v>479</v>
+        <v>195</v>
       </c>
       <c r="C59" t="s">
-        <v>189</v>
+        <v>480</v>
       </c>
       <c r="D59" t="s">
         <v>190</v>
       </c>
       <c r="E59" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F59" t="s">
-        <v>481</v>
+        <v>199</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>482</v>
@@ -4464,148 +5199,148 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>479</v>
+      </c>
+      <c r="B60" t="s">
+        <v>195</v>
+      </c>
+      <c r="C60" t="s">
+        <v>196</v>
+      </c>
+      <c r="D60" t="s">
+        <v>190</v>
+      </c>
+      <c r="E60" t="s">
+        <v>481</v>
+      </c>
+      <c r="F60" t="s">
+        <v>199</v>
+      </c>
+      <c r="H60" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="B60" t="s">
-        <v>484</v>
-      </c>
-      <c r="C60" t="s">
-        <v>485</v>
-      </c>
-      <c r="D60" t="s">
-        <v>197</v>
-      </c>
-      <c r="E60" t="s">
-        <v>486</v>
-      </c>
-      <c r="F60" t="s">
-        <v>211</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B61" t="s">
-        <v>489</v>
+        <v>195</v>
       </c>
       <c r="C61" t="s">
-        <v>490</v>
+        <v>215</v>
       </c>
       <c r="D61" t="s">
         <v>190</v>
       </c>
       <c r="E61" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="F61" t="s">
-        <v>492</v>
+        <v>199</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="B62" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="C62" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="D62" t="s">
         <v>197</v>
       </c>
       <c r="E62" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="F62" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="B63" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="C63" t="s">
-        <v>196</v>
+        <v>295</v>
       </c>
       <c r="D63" t="s">
         <v>190</v>
       </c>
       <c r="E63" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="F63" t="s">
-        <v>503</v>
+        <v>223</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>505</v>
+        <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>422</v>
+        <v>496</v>
       </c>
       <c r="C64" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="D64" t="s">
         <v>190</v>
       </c>
       <c r="E64" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="F64" t="s">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>509</v>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>422</v>
+        <v>501</v>
       </c>
       <c r="C65" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D65" t="s">
         <v>190</v>
       </c>
       <c r="E65" t="s">
-        <v>507</v>
+        <v>223</v>
       </c>
       <c r="F65" t="s">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="B66" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="C66" t="s">
         <v>189</v>
@@ -4614,240 +5349,240 @@
         <v>190</v>
       </c>
       <c r="E66" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="F66" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="B67" t="s">
-        <v>244</v>
+        <v>510</v>
       </c>
       <c r="C67" t="s">
-        <v>517</v>
+        <v>203</v>
       </c>
       <c r="D67" t="s">
         <v>190</v>
       </c>
       <c r="E67" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="F67" t="s">
-        <v>247</v>
+        <v>512</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>514</v>
+      </c>
+      <c r="B68" t="s">
+        <v>515</v>
+      </c>
+      <c r="C68" t="s">
+        <v>516</v>
+      </c>
+      <c r="D68" t="s">
+        <v>517</v>
+      </c>
+      <c r="E68" t="s">
+        <v>518</v>
+      </c>
+      <c r="F68" t="s">
+        <v>519</v>
+      </c>
+      <c r="H68" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="B68" t="s">
-        <v>256</v>
-      </c>
-      <c r="C68" t="s">
-        <v>203</v>
-      </c>
-      <c r="D68" t="s">
-        <v>190</v>
-      </c>
-      <c r="E68" t="s">
-        <v>521</v>
-      </c>
-      <c r="F68" t="s">
-        <v>522</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>521</v>
+      </c>
+      <c r="B69" t="s">
+        <v>522</v>
+      </c>
+      <c r="C69" t="s">
+        <v>295</v>
+      </c>
+      <c r="D69" t="s">
+        <v>190</v>
+      </c>
+      <c r="E69" t="s">
+        <v>523</v>
+      </c>
+      <c r="F69" t="s">
         <v>524</v>
       </c>
-      <c r="B69" t="s">
+      <c r="H69" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="C69" t="s">
-        <v>225</v>
-      </c>
-      <c r="D69" t="s">
-        <v>197</v>
-      </c>
-      <c r="E69" t="s">
-        <v>526</v>
-      </c>
-      <c r="F69" t="s">
-        <v>527</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>526</v>
+      </c>
+      <c r="B70" t="s">
+        <v>527</v>
+      </c>
+      <c r="C70" t="s">
+        <v>528</v>
+      </c>
+      <c r="D70" t="s">
+        <v>190</v>
+      </c>
+      <c r="E70" t="s">
         <v>529</v>
       </c>
-      <c r="B70" t="s">
+      <c r="F70" t="s">
+        <v>223</v>
+      </c>
+      <c r="H70" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="C70" t="s">
-        <v>196</v>
-      </c>
-      <c r="D70" t="s">
-        <v>372</v>
-      </c>
-      <c r="E70" t="s">
-        <v>518</v>
-      </c>
-      <c r="F70" t="s">
-        <v>531</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>531</v>
+      </c>
+      <c r="B71" t="s">
+        <v>532</v>
+      </c>
+      <c r="C71" t="s">
+        <v>203</v>
+      </c>
+      <c r="D71" t="s">
+        <v>190</v>
+      </c>
+      <c r="E71" t="s">
         <v>533</v>
       </c>
-      <c r="B71" t="s">
+      <c r="F71" t="s">
         <v>534</v>
       </c>
-      <c r="C71" t="s">
+      <c r="H71" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="D71" t="s">
-        <v>190</v>
-      </c>
-      <c r="E71" t="s">
-        <v>536</v>
-      </c>
-      <c r="F71" t="s">
-        <v>457</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>536</v>
+      </c>
+      <c r="B72" t="s">
+        <v>272</v>
+      </c>
+      <c r="C72" t="s">
+        <v>273</v>
+      </c>
+      <c r="D72" t="s">
+        <v>190</v>
+      </c>
+      <c r="E72" t="s">
+        <v>274</v>
+      </c>
+      <c r="F72" t="s">
+        <v>537</v>
+      </c>
+      <c r="H72" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="B72" t="s">
-        <v>534</v>
-      </c>
-      <c r="C72" t="s">
-        <v>535</v>
-      </c>
-      <c r="D72" t="s">
-        <v>190</v>
-      </c>
-      <c r="E72" t="s">
-        <v>539</v>
-      </c>
-      <c r="F72" t="s">
-        <v>457</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>539</v>
+      </c>
+      <c r="B73" t="s">
+        <v>540</v>
+      </c>
+      <c r="C73" t="s">
         <v>541</v>
       </c>
-      <c r="B73" t="s">
+      <c r="D73" t="s">
+        <v>190</v>
+      </c>
+      <c r="E73" t="s">
+        <v>494</v>
+      </c>
+      <c r="F73" t="s">
         <v>542</v>
       </c>
-      <c r="C73" t="s">
-        <v>278</v>
-      </c>
-      <c r="D73" t="s">
-        <v>190</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="H73" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="F73" t="s">
-        <v>544</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>544</v>
+      </c>
+      <c r="B74" t="s">
+        <v>545</v>
+      </c>
+      <c r="C74" t="s">
+        <v>189</v>
+      </c>
+      <c r="D74" t="s">
+        <v>190</v>
+      </c>
+      <c r="E74" t="s">
         <v>546</v>
       </c>
-      <c r="B74" t="s">
+      <c r="F74" t="s">
         <v>547</v>
       </c>
-      <c r="C74" t="s">
-        <v>407</v>
-      </c>
-      <c r="D74" t="s">
-        <v>190</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="H74" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="F74" t="s">
-        <v>549</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>549</v>
+      </c>
+      <c r="B75" t="s">
+        <v>522</v>
+      </c>
+      <c r="C75" t="s">
+        <v>377</v>
+      </c>
+      <c r="D75" t="s">
+        <v>190</v>
+      </c>
+      <c r="E75" t="s">
+        <v>523</v>
+      </c>
+      <c r="F75" t="s">
+        <v>550</v>
+      </c>
+      <c r="H75" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="B75" t="s">
-        <v>552</v>
-      </c>
-      <c r="C75" t="s">
-        <v>553</v>
-      </c>
-      <c r="D75" t="s">
-        <v>190</v>
-      </c>
-      <c r="E75" t="s">
-        <v>480</v>
-      </c>
-      <c r="F75" t="s">
-        <v>211</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>552</v>
+      </c>
+      <c r="B76" t="s">
+        <v>553</v>
+      </c>
+      <c r="C76" t="s">
+        <v>554</v>
+      </c>
+      <c r="D76" t="s">
+        <v>190</v>
+      </c>
+      <c r="E76" t="s">
         <v>555</v>
       </c>
-      <c r="B76" t="s">
-        <v>512</v>
-      </c>
-      <c r="C76" t="s">
-        <v>189</v>
-      </c>
-      <c r="D76" t="s">
-        <v>190</v>
-      </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>556</v>
-      </c>
-      <c r="F76" t="s">
-        <v>514</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>557</v>
@@ -4861,7 +5596,7 @@
         <v>559</v>
       </c>
       <c r="C77" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D77" t="s">
         <v>190</v>
@@ -4887,154 +5622,1488 @@
         <v>565</v>
       </c>
       <c r="D78" t="s">
+        <v>190</v>
+      </c>
+      <c r="E78" t="s">
         <v>566</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>567</v>
       </c>
-      <c r="F78" t="s">
+      <c r="H78" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B79" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C79" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D79" t="s">
-        <v>566</v>
+        <v>190</v>
       </c>
       <c r="E79" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F79" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B80" t="s">
-        <v>244</v>
+        <v>576</v>
       </c>
       <c r="C80" t="s">
-        <v>517</v>
+        <v>189</v>
       </c>
       <c r="D80" t="s">
         <v>190</v>
       </c>
       <c r="E80" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F80" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B81" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C81" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D81" t="s">
         <v>190</v>
       </c>
       <c r="E81" t="s">
-        <v>578</v>
+        <v>223</v>
       </c>
       <c r="F81" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B82" t="s">
-        <v>512</v>
+        <v>584</v>
       </c>
       <c r="C82" t="s">
-        <v>189</v>
+        <v>585</v>
       </c>
       <c r="D82" t="s">
         <v>190</v>
       </c>
       <c r="E82" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="F82" t="s">
-        <v>514</v>
+        <v>587</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B83" t="s">
-        <v>426</v>
+        <v>590</v>
       </c>
       <c r="C83" t="s">
-        <v>427</v>
+        <v>591</v>
       </c>
       <c r="D83" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E83" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="F83" t="s">
-        <v>429</v>
+        <v>593</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>595</v>
+      </c>
+      <c r="B84" t="s">
+        <v>590</v>
+      </c>
+      <c r="C84" t="s">
+        <v>591</v>
+      </c>
+      <c r="D84" t="s">
+        <v>190</v>
+      </c>
+      <c r="E84" t="s">
+        <v>596</v>
+      </c>
+      <c r="F84" t="s">
+        <v>597</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>599</v>
+      </c>
+      <c r="B85" t="s">
+        <v>600</v>
+      </c>
+      <c r="C85" t="s">
+        <v>215</v>
+      </c>
+      <c r="D85" t="s">
+        <v>190</v>
+      </c>
+      <c r="E85" t="s">
+        <v>601</v>
+      </c>
+      <c r="F85" t="s">
+        <v>602</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>604</v>
+      </c>
+      <c r="B86" t="s">
+        <v>605</v>
+      </c>
+      <c r="C86" t="s">
+        <v>203</v>
+      </c>
+      <c r="D86" t="s">
+        <v>190</v>
+      </c>
+      <c r="E86" t="s">
+        <v>606</v>
+      </c>
+      <c r="F86" t="s">
+        <v>291</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>608</v>
+      </c>
+      <c r="B87" t="s">
+        <v>609</v>
+      </c>
+      <c r="C87" t="s">
+        <v>215</v>
+      </c>
+      <c r="D87" t="s">
+        <v>190</v>
+      </c>
+      <c r="E87" t="s">
+        <v>610</v>
+      </c>
+      <c r="F87" t="s">
+        <v>611</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>613</v>
+      </c>
+      <c r="B88" t="s">
+        <v>614</v>
+      </c>
+      <c r="C88" t="s">
+        <v>247</v>
+      </c>
+      <c r="D88" t="s">
+        <v>190</v>
+      </c>
+      <c r="E88" t="s">
+        <v>615</v>
+      </c>
+      <c r="F88" t="s">
+        <v>616</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>618</v>
+      </c>
+      <c r="B89" t="s">
+        <v>614</v>
+      </c>
+      <c r="C89" t="s">
+        <v>247</v>
+      </c>
+      <c r="D89" t="s">
+        <v>190</v>
+      </c>
+      <c r="E89" t="s">
+        <v>615</v>
+      </c>
+      <c r="F89" t="s">
+        <v>616</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>620</v>
+      </c>
+      <c r="B90" t="s">
+        <v>408</v>
+      </c>
+      <c r="C90" t="s">
+        <v>409</v>
+      </c>
+      <c r="D90" t="s">
+        <v>190</v>
+      </c>
+      <c r="E90" t="s">
+        <v>621</v>
+      </c>
+      <c r="F90" t="s">
+        <v>411</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>623</v>
+      </c>
+      <c r="B91" t="s">
+        <v>624</v>
+      </c>
+      <c r="C91" t="s">
+        <v>625</v>
+      </c>
+      <c r="D91" t="s">
+        <v>190</v>
+      </c>
+      <c r="E91" t="s">
+        <v>626</v>
+      </c>
+      <c r="F91" t="s">
+        <v>627</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>629</v>
+      </c>
+      <c r="B92" t="s">
+        <v>584</v>
+      </c>
+      <c r="C92" t="s">
+        <v>630</v>
+      </c>
+      <c r="D92" t="s">
+        <v>190</v>
+      </c>
+      <c r="E92" t="s">
+        <v>586</v>
+      </c>
+      <c r="F92" t="s">
+        <v>631</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>633</v>
+      </c>
+      <c r="B93" t="s">
+        <v>634</v>
+      </c>
+      <c r="C93" t="s">
+        <v>189</v>
+      </c>
+      <c r="D93" t="s">
+        <v>190</v>
+      </c>
+      <c r="E93" t="s">
+        <v>635</v>
+      </c>
+      <c r="F93" t="s">
+        <v>636</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>638</v>
+      </c>
+      <c r="B94" t="s">
+        <v>639</v>
+      </c>
+      <c r="C94" t="s">
+        <v>640</v>
+      </c>
+      <c r="D94" t="s">
+        <v>222</v>
+      </c>
+      <c r="E94" t="s">
+        <v>641</v>
+      </c>
+      <c r="F94" t="s">
+        <v>642</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>644</v>
+      </c>
+      <c r="B95" t="s">
+        <v>300</v>
+      </c>
+      <c r="C95" t="s">
+        <v>645</v>
+      </c>
+      <c r="D95" t="s">
+        <v>190</v>
+      </c>
+      <c r="E95" t="s">
+        <v>301</v>
+      </c>
+      <c r="F95" t="s">
+        <v>302</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>647</v>
+      </c>
+      <c r="B96" t="s">
+        <v>251</v>
+      </c>
+      <c r="C96" t="s">
+        <v>295</v>
+      </c>
+      <c r="D96" t="s">
+        <v>190</v>
+      </c>
+      <c r="E96" t="s">
+        <v>648</v>
+      </c>
+      <c r="F96" t="s">
+        <v>253</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>650</v>
+      </c>
+      <c r="B97" t="s">
+        <v>651</v>
+      </c>
+      <c r="C97" t="s">
+        <v>652</v>
+      </c>
+      <c r="D97" t="s">
+        <v>190</v>
+      </c>
+      <c r="E97" t="s">
+        <v>653</v>
+      </c>
+      <c r="F97" t="s">
+        <v>223</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>655</v>
+      </c>
+      <c r="B98" t="s">
+        <v>656</v>
+      </c>
+      <c r="C98" t="s">
+        <v>203</v>
+      </c>
+      <c r="D98" t="s">
+        <v>222</v>
+      </c>
+      <c r="E98" t="s">
+        <v>657</v>
+      </c>
+      <c r="F98" t="s">
+        <v>658</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>660</v>
+      </c>
+      <c r="B99" t="s">
+        <v>661</v>
+      </c>
+      <c r="C99" t="s">
+        <v>662</v>
+      </c>
+      <c r="D99" t="s">
+        <v>197</v>
+      </c>
+      <c r="E99" t="s">
+        <v>663</v>
+      </c>
+      <c r="F99" t="s">
+        <v>664</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>666</v>
+      </c>
+      <c r="B100" t="s">
+        <v>667</v>
+      </c>
+      <c r="C100" t="s">
+        <v>189</v>
+      </c>
+      <c r="D100" t="s">
+        <v>190</v>
+      </c>
+      <c r="E100" t="s">
+        <v>668</v>
+      </c>
+      <c r="F100" t="s">
+        <v>669</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>671</v>
+      </c>
+      <c r="B101" t="s">
+        <v>672</v>
+      </c>
+      <c r="C101" t="s">
+        <v>673</v>
+      </c>
+      <c r="D101" t="s">
+        <v>197</v>
+      </c>
+      <c r="E101" t="s">
+        <v>322</v>
+      </c>
+      <c r="F101" t="s">
+        <v>674</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>676</v>
+      </c>
+      <c r="B102" t="s">
+        <v>677</v>
+      </c>
+      <c r="C102" t="s">
+        <v>678</v>
+      </c>
+      <c r="D102" t="s">
+        <v>197</v>
+      </c>
+      <c r="E102" t="s">
+        <v>679</v>
+      </c>
+      <c r="F102" t="s">
+        <v>223</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>681</v>
+      </c>
+      <c r="B103" t="s">
+        <v>682</v>
+      </c>
+      <c r="C103" t="s">
+        <v>247</v>
+      </c>
+      <c r="D103" t="s">
+        <v>190</v>
+      </c>
+      <c r="E103" t="s">
+        <v>683</v>
+      </c>
+      <c r="F103" t="s">
+        <v>684</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>686</v>
+      </c>
+      <c r="B104" t="s">
+        <v>300</v>
+      </c>
+      <c r="C104" t="s">
+        <v>377</v>
+      </c>
+      <c r="D104" t="s">
+        <v>190</v>
+      </c>
+      <c r="E104" t="s">
+        <v>523</v>
+      </c>
+      <c r="F104" t="s">
+        <v>302</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>688</v>
+      </c>
+      <c r="B105" t="s">
+        <v>689</v>
+      </c>
+      <c r="C105" t="s">
+        <v>690</v>
+      </c>
+      <c r="D105" t="s">
+        <v>190</v>
+      </c>
+      <c r="E105" t="s">
+        <v>691</v>
+      </c>
+      <c r="F105" t="s">
+        <v>692</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>694</v>
+      </c>
+      <c r="B106" t="s">
+        <v>695</v>
+      </c>
+      <c r="C106" t="s">
+        <v>696</v>
+      </c>
+      <c r="D106" t="s">
+        <v>197</v>
+      </c>
+      <c r="E106" t="s">
+        <v>328</v>
+      </c>
+      <c r="F106" t="s">
+        <v>199</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>698</v>
+      </c>
+      <c r="B107" t="s">
+        <v>699</v>
+      </c>
+      <c r="C107" t="s">
+        <v>295</v>
+      </c>
+      <c r="D107" t="s">
+        <v>190</v>
+      </c>
+      <c r="E107" t="s">
+        <v>700</v>
+      </c>
+      <c r="F107" t="s">
+        <v>701</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>703</v>
+      </c>
+      <c r="B108" t="s">
+        <v>704</v>
+      </c>
+      <c r="C108" t="s">
+        <v>203</v>
+      </c>
+      <c r="D108" t="s">
+        <v>190</v>
+      </c>
+      <c r="E108" t="s">
+        <v>705</v>
+      </c>
+      <c r="F108" t="s">
+        <v>706</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>708</v>
+      </c>
+      <c r="B109" t="s">
+        <v>580</v>
+      </c>
+      <c r="C109" t="s">
+        <v>709</v>
+      </c>
+      <c r="D109" t="s">
+        <v>190</v>
+      </c>
+      <c r="E109" t="s">
+        <v>710</v>
+      </c>
+      <c r="F109" t="s">
+        <v>581</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>712</v>
+      </c>
+      <c r="B110" t="s">
+        <v>580</v>
+      </c>
+      <c r="C110" t="s">
+        <v>709</v>
+      </c>
+      <c r="D110" t="s">
+        <v>190</v>
+      </c>
+      <c r="E110" t="s">
+        <v>710</v>
+      </c>
+      <c r="F110" t="s">
+        <v>581</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>714</v>
+      </c>
+      <c r="B111" t="s">
+        <v>715</v>
+      </c>
+      <c r="C111" t="s">
+        <v>209</v>
+      </c>
+      <c r="D111" t="s">
+        <v>197</v>
+      </c>
+      <c r="E111" t="s">
+        <v>716</v>
+      </c>
+      <c r="F111" t="s">
+        <v>717</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>719</v>
+      </c>
+      <c r="B112" t="s">
+        <v>720</v>
+      </c>
+      <c r="C112" t="s">
+        <v>203</v>
+      </c>
+      <c r="D112" t="s">
+        <v>190</v>
+      </c>
+      <c r="E112" t="s">
+        <v>721</v>
+      </c>
+      <c r="F112" t="s">
+        <v>373</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>723</v>
+      </c>
+      <c r="B113" t="s">
+        <v>724</v>
+      </c>
+      <c r="C113" t="s">
+        <v>189</v>
+      </c>
+      <c r="D113" t="s">
+        <v>190</v>
+      </c>
+      <c r="E113" t="s">
+        <v>725</v>
+      </c>
+      <c r="F113" t="s">
+        <v>726</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>728</v>
+      </c>
+      <c r="B114" t="s">
+        <v>272</v>
+      </c>
+      <c r="C114" t="s">
+        <v>729</v>
+      </c>
+      <c r="D114" t="s">
+        <v>190</v>
+      </c>
+      <c r="E114" t="s">
+        <v>606</v>
+      </c>
+      <c r="F114" t="s">
+        <v>275</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>731</v>
+      </c>
+      <c r="B115" t="s">
+        <v>311</v>
+      </c>
+      <c r="C115" t="s">
+        <v>209</v>
+      </c>
+      <c r="D115" t="s">
+        <v>190</v>
+      </c>
+      <c r="E115" t="s">
+        <v>732</v>
+      </c>
+      <c r="F115" t="s">
+        <v>733</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>735</v>
+      </c>
+      <c r="B116" t="s">
+        <v>736</v>
+      </c>
+      <c r="C116" t="s">
+        <v>247</v>
+      </c>
+      <c r="D116" t="s">
+        <v>197</v>
+      </c>
+      <c r="E116" t="s">
+        <v>737</v>
+      </c>
+      <c r="F116" t="s">
+        <v>389</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>739</v>
+      </c>
+      <c r="B117" t="s">
+        <v>740</v>
+      </c>
+      <c r="C117" t="s">
+        <v>203</v>
+      </c>
+      <c r="D117" t="s">
+        <v>517</v>
+      </c>
+      <c r="E117" t="s">
+        <v>606</v>
+      </c>
+      <c r="F117" t="s">
+        <v>741</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>743</v>
+      </c>
+      <c r="B118" t="s">
+        <v>744</v>
+      </c>
+      <c r="C118" t="s">
+        <v>203</v>
+      </c>
+      <c r="D118" t="s">
+        <v>190</v>
+      </c>
+      <c r="E118" t="s">
+        <v>745</v>
+      </c>
+      <c r="F118" t="s">
+        <v>746</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>748</v>
+      </c>
+      <c r="B119" t="s">
+        <v>493</v>
+      </c>
+      <c r="C119" t="s">
+        <v>295</v>
+      </c>
+      <c r="D119" t="s">
+        <v>190</v>
+      </c>
+      <c r="E119" t="s">
+        <v>749</v>
+      </c>
+      <c r="F119" t="s">
+        <v>750</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>752</v>
+      </c>
+      <c r="B120" t="s">
+        <v>753</v>
+      </c>
+      <c r="C120" t="s">
+        <v>754</v>
+      </c>
+      <c r="D120" t="s">
+        <v>190</v>
+      </c>
+      <c r="E120" t="s">
+        <v>755</v>
+      </c>
+      <c r="F120" t="s">
+        <v>631</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>757</v>
+      </c>
+      <c r="B121" t="s">
+        <v>753</v>
+      </c>
+      <c r="C121" t="s">
+        <v>754</v>
+      </c>
+      <c r="D121" t="s">
+        <v>190</v>
+      </c>
+      <c r="E121" t="s">
+        <v>758</v>
+      </c>
+      <c r="F121" t="s">
+        <v>631</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>760</v>
+      </c>
+      <c r="B122" t="s">
+        <v>294</v>
+      </c>
+      <c r="C122" t="s">
+        <v>295</v>
+      </c>
+      <c r="D122" t="s">
+        <v>190</v>
+      </c>
+      <c r="E122" t="s">
+        <v>761</v>
+      </c>
+      <c r="F122" t="s">
+        <v>297</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>763</v>
+      </c>
+      <c r="B123" t="s">
+        <v>764</v>
+      </c>
+      <c r="C123" t="s">
+        <v>189</v>
+      </c>
+      <c r="D123" t="s">
+        <v>190</v>
+      </c>
+      <c r="E123" t="s">
+        <v>372</v>
+      </c>
+      <c r="F123" t="s">
+        <v>765</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>767</v>
+      </c>
+      <c r="B124" t="s">
+        <v>768</v>
+      </c>
+      <c r="C124" t="s">
+        <v>295</v>
+      </c>
+      <c r="D124" t="s">
+        <v>190</v>
+      </c>
+      <c r="E124" t="s">
+        <v>769</v>
+      </c>
+      <c r="F124" t="s">
+        <v>770</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>772</v>
+      </c>
+      <c r="B125" t="s">
+        <v>773</v>
+      </c>
+      <c r="C125" t="s">
+        <v>565</v>
+      </c>
+      <c r="D125" t="s">
+        <v>190</v>
+      </c>
+      <c r="E125" t="s">
+        <v>774</v>
+      </c>
+      <c r="F125" t="s">
+        <v>775</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>777</v>
+      </c>
+      <c r="B126" t="s">
+        <v>778</v>
+      </c>
+      <c r="C126" t="s">
+        <v>779</v>
+      </c>
+      <c r="D126" t="s">
+        <v>190</v>
+      </c>
+      <c r="E126" t="s">
+        <v>668</v>
+      </c>
+      <c r="F126" t="s">
+        <v>223</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>781</v>
+      </c>
+      <c r="B127" t="s">
+        <v>724</v>
+      </c>
+      <c r="C127" t="s">
+        <v>189</v>
+      </c>
+      <c r="D127" t="s">
+        <v>190</v>
+      </c>
+      <c r="E127" t="s">
+        <v>782</v>
+      </c>
+      <c r="F127" t="s">
+        <v>726</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>784</v>
+      </c>
+      <c r="B128" t="s">
+        <v>614</v>
+      </c>
+      <c r="C128" t="s">
+        <v>247</v>
+      </c>
+      <c r="D128" t="s">
+        <v>190</v>
+      </c>
+      <c r="E128" t="s">
+        <v>785</v>
+      </c>
+      <c r="F128" t="s">
+        <v>616</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>787</v>
+      </c>
+      <c r="B129" t="s">
+        <v>614</v>
+      </c>
+      <c r="C129" t="s">
+        <v>788</v>
+      </c>
+      <c r="D129" t="s">
+        <v>190</v>
+      </c>
+      <c r="E129" t="s">
+        <v>785</v>
+      </c>
+      <c r="F129" t="s">
+        <v>616</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>787</v>
+      </c>
+      <c r="B130" t="s">
+        <v>614</v>
+      </c>
+      <c r="C130" t="s">
+        <v>247</v>
+      </c>
+      <c r="D130" t="s">
+        <v>190</v>
+      </c>
+      <c r="E130" t="s">
+        <v>785</v>
+      </c>
+      <c r="F130" t="s">
+        <v>616</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>787</v>
+      </c>
+      <c r="B131" t="s">
+        <v>614</v>
+      </c>
+      <c r="C131" t="s">
+        <v>791</v>
+      </c>
+      <c r="D131" t="s">
+        <v>190</v>
+      </c>
+      <c r="E131" t="s">
+        <v>785</v>
+      </c>
+      <c r="F131" t="s">
+        <v>616</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>793</v>
+      </c>
+      <c r="B132" t="s">
+        <v>794</v>
+      </c>
+      <c r="C132" t="s">
+        <v>203</v>
+      </c>
+      <c r="D132" t="s">
+        <v>190</v>
+      </c>
+      <c r="E132" t="s">
+        <v>795</v>
+      </c>
+      <c r="F132" t="s">
+        <v>796</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>798</v>
+      </c>
+      <c r="B133" t="s">
+        <v>799</v>
+      </c>
+      <c r="C133" t="s">
+        <v>800</v>
+      </c>
+      <c r="D133" t="s">
+        <v>267</v>
+      </c>
+      <c r="E133" t="s">
+        <v>801</v>
+      </c>
+      <c r="F133" t="s">
+        <v>802</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>798</v>
+      </c>
+      <c r="B134" t="s">
+        <v>799</v>
+      </c>
+      <c r="C134" t="s">
+        <v>804</v>
+      </c>
+      <c r="D134" t="s">
+        <v>267</v>
+      </c>
+      <c r="E134" t="s">
+        <v>345</v>
+      </c>
+      <c r="F134" t="s">
+        <v>802</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>806</v>
+      </c>
+      <c r="B135" t="s">
+        <v>807</v>
+      </c>
+      <c r="C135" t="s">
+        <v>247</v>
+      </c>
+      <c r="D135" t="s">
+        <v>267</v>
+      </c>
+      <c r="E135" t="s">
+        <v>808</v>
+      </c>
+      <c r="F135" t="s">
+        <v>234</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>810</v>
+      </c>
+      <c r="B136" t="s">
+        <v>272</v>
+      </c>
+      <c r="C136" t="s">
+        <v>729</v>
+      </c>
+      <c r="D136" t="s">
+        <v>190</v>
+      </c>
+      <c r="E136" t="s">
+        <v>811</v>
+      </c>
+      <c r="F136" t="s">
+        <v>275</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>813</v>
+      </c>
+      <c r="B137" t="s">
+        <v>814</v>
+      </c>
+      <c r="C137" t="s">
+        <v>203</v>
+      </c>
+      <c r="D137" t="s">
+        <v>190</v>
+      </c>
+      <c r="E137" t="s">
+        <v>815</v>
+      </c>
+      <c r="F137" t="s">
+        <v>816</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>818</v>
+      </c>
+      <c r="B138" t="s">
+        <v>724</v>
+      </c>
+      <c r="C138" t="s">
+        <v>189</v>
+      </c>
+      <c r="D138" t="s">
+        <v>190</v>
+      </c>
+      <c r="E138" t="s">
+        <v>819</v>
+      </c>
+      <c r="F138" t="s">
+        <v>726</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>821</v>
+      </c>
+      <c r="B139" t="s">
+        <v>584</v>
+      </c>
+      <c r="C139" t="s">
+        <v>585</v>
+      </c>
+      <c r="D139" t="s">
+        <v>197</v>
+      </c>
+      <c r="E139" t="s">
+        <v>822</v>
+      </c>
+      <c r="F139" t="s">
         <v>587</v>
       </c>
-      <c r="B84" t="s">
-        <v>588</v>
-      </c>
-      <c r="C84" t="s">
-        <v>278</v>
-      </c>
-      <c r="D84" t="s">
-        <v>566</v>
-      </c>
-      <c r="E84" t="s">
-        <v>589</v>
-      </c>
-      <c r="F84" t="s">
-        <v>590</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>591</v>
+      <c r="H139" s="2" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>824</v>
+      </c>
+      <c r="B140" t="s">
+        <v>825</v>
+      </c>
+      <c r="C140" t="s">
+        <v>826</v>
+      </c>
+      <c r="D140" t="s">
+        <v>190</v>
+      </c>
+      <c r="E140" t="s">
+        <v>827</v>
+      </c>
+      <c r="F140" t="s">
+        <v>828</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>830</v>
+      </c>
+      <c r="B141" t="s">
+        <v>831</v>
+      </c>
+      <c r="C141" t="s">
+        <v>295</v>
+      </c>
+      <c r="D141" t="s">
+        <v>267</v>
+      </c>
+      <c r="E141" t="s">
+        <v>832</v>
+      </c>
+      <c r="F141" t="s">
+        <v>833</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>835</v>
+      </c>
+      <c r="B142" t="s">
+        <v>522</v>
+      </c>
+      <c r="C142" t="s">
+        <v>338</v>
+      </c>
+      <c r="D142" t="s">
+        <v>190</v>
+      </c>
+      <c r="E142" t="s">
+        <v>301</v>
+      </c>
+      <c r="F142" t="s">
+        <v>302</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>836</v>
       </c>
     </row>
   </sheetData>
@@ -5123,6 +7192,64 @@
     <hyperlink ref="H82" r:id="rId81"/>
     <hyperlink ref="H83" r:id="rId82"/>
     <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
